--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136320478</v>
       </c>
       <c r="B5" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453642</v>
       </c>
       <c r="B6" t="n">
-        <v>92281</v>
+        <v>92284</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453551</v>
       </c>
       <c r="B7" t="n">
-        <v>92024</v>
+        <v>92027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>92024</v>
+        <v>92027</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136453594</v>
       </c>
       <c r="B9" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136453596</v>
       </c>
       <c r="B10" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136453598</v>
       </c>
       <c r="B11" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136453600</v>
       </c>
       <c r="B12" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136453602</v>
       </c>
       <c r="B13" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136453637</v>
       </c>
       <c r="B14" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>136453640</v>
       </c>
       <c r="B15" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136320486</v>
       </c>
       <c r="B16" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136453625</v>
       </c>
       <c r="B17" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>136453626</v>
       </c>
       <c r="B18" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136453627</v>
       </c>
       <c r="B19" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>136320487</v>
       </c>
       <c r="B20" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>136453653</v>
       </c>
       <c r="B21" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136453654</v>
       </c>
       <c r="B22" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>136320479</v>
       </c>
       <c r="B23" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136453646</v>
       </c>
       <c r="B24" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136453647</v>
       </c>
       <c r="B25" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136453648</v>
       </c>
       <c r="B26" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136453649</v>
       </c>
       <c r="B27" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136453650</v>
       </c>
       <c r="B28" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136453651</v>
       </c>
       <c r="B29" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136320475</v>
       </c>
       <c r="B30" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>136320484</v>
       </c>
       <c r="B31" t="n">
-        <v>93404</v>
+        <v>93407</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136453604</v>
       </c>
       <c r="B32" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136453606</v>
       </c>
       <c r="B33" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136453608</v>
       </c>
       <c r="B34" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136453610</v>
       </c>
       <c r="B35" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136453589</v>
       </c>
       <c r="B36" t="n">
-        <v>93044</v>
+        <v>93047</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>136453631</v>
       </c>
       <c r="B37" t="n">
-        <v>90701</v>
+        <v>90703</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>136453634</v>
       </c>
       <c r="B38" t="n">
-        <v>90701</v>
+        <v>90703</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136453635</v>
       </c>
       <c r="B39" t="n">
-        <v>90701</v>
+        <v>90703</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>136453636</v>
       </c>
       <c r="B40" t="n">
-        <v>90701</v>
+        <v>90703</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>136453592</v>
       </c>
       <c r="B41" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>136320482</v>
       </c>
       <c r="B42" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>136320483</v>
       </c>
       <c r="B43" t="n">
-        <v>93384</v>
+        <v>93387</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136453616</v>
       </c>
       <c r="B50" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>136453618</v>
       </c>
       <c r="B51" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>136453620</v>
       </c>
       <c r="B52" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>136453622</v>
       </c>
       <c r="B53" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>136453623</v>
       </c>
       <c r="B54" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136320478</v>
       </c>
       <c r="B5" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453642</v>
       </c>
       <c r="B6" t="n">
-        <v>92284</v>
+        <v>92285</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453551</v>
       </c>
       <c r="B7" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136320486</v>
       </c>
       <c r="B16" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136453625</v>
       </c>
       <c r="B17" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>136453626</v>
       </c>
       <c r="B18" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136453627</v>
       </c>
       <c r="B19" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>136320487</v>
       </c>
       <c r="B20" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>136453653</v>
       </c>
       <c r="B21" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136453654</v>
       </c>
       <c r="B22" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>136320479</v>
       </c>
       <c r="B23" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136453646</v>
       </c>
       <c r="B24" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136453647</v>
       </c>
       <c r="B25" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136453648</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136453649</v>
       </c>
       <c r="B27" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136453650</v>
       </c>
       <c r="B28" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136453651</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136320475</v>
       </c>
       <c r="B30" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>136320484</v>
       </c>
       <c r="B31" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136453604</v>
       </c>
       <c r="B32" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136453606</v>
       </c>
       <c r="B33" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136453608</v>
       </c>
       <c r="B34" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136453610</v>
       </c>
       <c r="B35" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136453589</v>
       </c>
       <c r="B36" t="n">
-        <v>93047</v>
+        <v>93048</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>136453592</v>
       </c>
       <c r="B41" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>136320483</v>
       </c>
       <c r="B43" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136453616</v>
       </c>
       <c r="B50" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>136453618</v>
       </c>
       <c r="B51" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>136453620</v>
       </c>
       <c r="B52" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>136453622</v>
       </c>
       <c r="B53" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>136453623</v>
       </c>
       <c r="B54" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320481</v>
       </c>
       <c r="B4" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136320478</v>
       </c>
       <c r="B5" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1135,7 +1135,7 @@
         <v>136453642</v>
       </c>
       <c r="B6" t="n">
-        <v>92285</v>
+        <v>92290</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1237,7 +1237,7 @@
         <v>136453551</v>
       </c>
       <c r="B7" t="n">
-        <v>92028</v>
+        <v>92033</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136453553</v>
       </c>
       <c r="B8" t="n">
-        <v>92028</v>
+        <v>92033</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
         <v>136453594</v>
       </c>
       <c r="B9" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>136453596</v>
       </c>
       <c r="B10" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1645,7 +1645,7 @@
         <v>136453598</v>
       </c>
       <c r="B11" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>136453600</v>
       </c>
       <c r="B12" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>136453602</v>
       </c>
       <c r="B13" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>136453637</v>
       </c>
       <c r="B14" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2053,7 +2053,7 @@
         <v>136453640</v>
       </c>
       <c r="B15" t="n">
-        <v>87499</v>
+        <v>87501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2155,7 +2155,7 @@
         <v>136320486</v>
       </c>
       <c r="B16" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,7 +2267,7 @@
         <v>136453625</v>
       </c>
       <c r="B17" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>136453626</v>
       </c>
       <c r="B18" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2471,7 +2471,7 @@
         <v>136453627</v>
       </c>
       <c r="B19" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>136320487</v>
       </c>
       <c r="B20" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>136453653</v>
       </c>
       <c r="B21" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>136453654</v>
       </c>
       <c r="B22" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,7 +2905,7 @@
         <v>136320479</v>
       </c>
       <c r="B23" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3017,7 +3017,7 @@
         <v>136453646</v>
       </c>
       <c r="B24" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>136453647</v>
       </c>
       <c r="B25" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3221,7 +3221,7 @@
         <v>136453648</v>
       </c>
       <c r="B26" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3323,7 +3323,7 @@
         <v>136453649</v>
       </c>
       <c r="B27" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>136453650</v>
       </c>
       <c r="B28" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>136453651</v>
       </c>
       <c r="B29" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3629,7 +3629,7 @@
         <v>136320475</v>
       </c>
       <c r="B30" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>136320484</v>
       </c>
       <c r="B31" t="n">
-        <v>93408</v>
+        <v>93413</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
         <v>136453604</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         <v>136453606</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,7 +4057,7 @@
         <v>136453608</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
         <v>136453610</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>136453589</v>
       </c>
       <c r="B36" t="n">
-        <v>93048</v>
+        <v>93053</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>136453631</v>
       </c>
       <c r="B37" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>136453634</v>
       </c>
       <c r="B38" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>136453635</v>
       </c>
       <c r="B39" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4670,7 +4670,7 @@
         <v>136453636</v>
       </c>
       <c r="B40" t="n">
-        <v>90703</v>
+        <v>90705</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>136453592</v>
       </c>
       <c r="B41" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4874,7 +4874,7 @@
         <v>136320482</v>
       </c>
       <c r="B42" t="n">
-        <v>91463</v>
+        <v>91465</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>136320483</v>
       </c>
       <c r="B43" t="n">
-        <v>93388</v>
+        <v>93393</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>136453628</v>
       </c>
       <c r="B44" t="n">
-        <v>79498</v>
+        <v>79500</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>136453655</v>
       </c>
       <c r="B45" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>136453656</v>
       </c>
       <c r="B46" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>136453555</v>
       </c>
       <c r="B47" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         <v>136453629</v>
       </c>
       <c r="B48" t="n">
-        <v>80593</v>
+        <v>80595</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>136453641</v>
       </c>
       <c r="B49" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         <v>136453616</v>
       </c>
       <c r="B50" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5817,7 +5817,7 @@
         <v>136453618</v>
       </c>
       <c r="B51" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5919,7 +5919,7 @@
         <v>136453620</v>
       </c>
       <c r="B52" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6021,7 +6021,7 @@
         <v>136453622</v>
       </c>
       <c r="B53" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>136453623</v>
       </c>
       <c r="B54" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>136453575</v>
       </c>
       <c r="B55" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>136453577</v>
       </c>
       <c r="B56" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6429,7 +6429,7 @@
         <v>136453579</v>
       </c>
       <c r="B57" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>136453581</v>
       </c>
       <c r="B58" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6633,7 +6633,7 @@
         <v>136453583</v>
       </c>
       <c r="B59" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6735,7 +6735,7 @@
         <v>136453585</v>
       </c>
       <c r="B60" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>136453587</v>
       </c>
       <c r="B61" t="n">
-        <v>79497</v>
+        <v>79499</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ61"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,48 +1016,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136320478</v>
+        <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>92290</v>
+        <v>79142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>688611</v>
+        <v>688705</v>
       </c>
       <c r="R5" t="n">
-        <v>7412672</v>
+        <v>7413042</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1089,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,69 +1105,68 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320478</t>
+          <t>https://artportalen.se/Sighting/136814462</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136453642</v>
+        <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>92290</v>
+        <v>79142</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>688653</v>
+        <v>688552</v>
       </c>
       <c r="R6" t="n">
-        <v>7413090</v>
+        <v>7413025</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1200,9 +1196,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1217,62 +1223,65 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453642</t>
+          <t>https://artportalen.se/Sighting/136814470</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136453551</v>
+        <v>136320478</v>
       </c>
       <c r="B7" t="n">
-        <v>92033</v>
+        <v>92290</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>688774</v>
+        <v>688611</v>
       </c>
       <c r="R7" t="n">
-        <v>7412730</v>
+        <v>7412672</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1302,24 +1311,35 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1330,38 +1350,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453551</t>
+          <t>https://artportalen.se/Sighting/136320478</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136453553</v>
+        <v>136453642</v>
       </c>
       <c r="B8" t="n">
-        <v>92033</v>
+        <v>92290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3242</v>
+        <v>1503</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1371,10 +1391,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>688682</v>
+        <v>688653</v>
       </c>
       <c r="R8" t="n">
-        <v>7412631</v>
+        <v>7413090</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1432,16 +1452,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453553</t>
+          <t>https://artportalen.se/Sighting/136453642</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136453594</v>
+        <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>87501</v>
+        <v>91115</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1449,37 +1469,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>688586</v>
+        <v>688747</v>
       </c>
       <c r="R9" t="n">
-        <v>7413077</v>
+        <v>7412648</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1506,9 +1526,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1523,27 +1553,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453594</t>
+          <t>https://artportalen.se/Sighting/136814445</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136453596</v>
+        <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>87501</v>
+        <v>91115</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,34 +1581,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3690</v>
+        <v>1962</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>688705</v>
+        <v>688674</v>
       </c>
       <c r="R10" t="n">
-        <v>7412751</v>
+        <v>7412730</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1608,9 +1638,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:13</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1625,27 +1665,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453596</t>
+          <t>https://artportalen.se/Sighting/136814450</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136453598</v>
+        <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>87501</v>
+        <v>93434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,34 +1693,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3690</v>
+        <v>3100</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>688374</v>
+        <v>688667</v>
       </c>
       <c r="R11" t="n">
-        <v>7412855</v>
+        <v>7412594</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1710,9 +1750,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1727,27 +1777,27 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453598</t>
+          <t>https://artportalen.se/Sighting/136814441</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136453600</v>
+        <v>136453551</v>
       </c>
       <c r="B12" t="n">
-        <v>87501</v>
+        <v>92033</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1755,21 +1805,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3690</v>
+        <v>3242</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1779,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>688737</v>
+        <v>688774</v>
       </c>
       <c r="R12" t="n">
-        <v>7413029</v>
+        <v>7412730</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,16 +1890,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453600</t>
+          <t>https://artportalen.se/Sighting/136453551</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136453602</v>
+        <v>136453553</v>
       </c>
       <c r="B13" t="n">
-        <v>87501</v>
+        <v>92033</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,21 +1907,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3690</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1881,10 +1931,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>688702</v>
+        <v>688682</v>
       </c>
       <c r="R13" t="n">
-        <v>7412735</v>
+        <v>7412631</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1942,13 +1992,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453602</t>
+          <t>https://artportalen.se/Sighting/136453553</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136453637</v>
+        <v>136453594</v>
       </c>
       <c r="B14" t="n">
         <v>87501</v>
@@ -1983,10 +2033,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>688710</v>
+        <v>688586</v>
       </c>
       <c r="R14" t="n">
-        <v>7412627</v>
+        <v>7413077</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2044,13 +2094,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453637</t>
+          <t>https://artportalen.se/Sighting/136453594</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136453640</v>
+        <v>136453596</v>
       </c>
       <c r="B15" t="n">
         <v>87501</v>
@@ -2085,10 +2135,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>688802</v>
+        <v>688705</v>
       </c>
       <c r="R15" t="n">
-        <v>7412543</v>
+        <v>7412751</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2146,16 +2196,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453640</t>
+          <t>https://artportalen.se/Sighting/136453596</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136320486</v>
+        <v>136453598</v>
       </c>
       <c r="B16" t="n">
-        <v>93401</v>
+        <v>87501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,21 +2213,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2187,10 +2237,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>688598</v>
+        <v>688374</v>
       </c>
       <c r="R16" t="n">
-        <v>7412746</v>
+        <v>7412855</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2220,19 +2270,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>12:52</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,7 +2287,7 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
@@ -2258,16 +2298,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320486</t>
+          <t>https://artportalen.se/Sighting/136453598</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136453625</v>
+        <v>136453600</v>
       </c>
       <c r="B17" t="n">
-        <v>93401</v>
+        <v>87501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2275,21 +2315,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2299,10 +2339,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>688757</v>
+        <v>688737</v>
       </c>
       <c r="R17" t="n">
-        <v>7413031</v>
+        <v>7413029</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2360,16 +2400,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453625</t>
+          <t>https://artportalen.se/Sighting/136453600</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136453626</v>
+        <v>136453602</v>
       </c>
       <c r="B18" t="n">
-        <v>93401</v>
+        <v>87501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2377,21 +2417,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2401,10 +2441,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>688732</v>
+        <v>688702</v>
       </c>
       <c r="R18" t="n">
-        <v>7412730</v>
+        <v>7412735</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2462,16 +2502,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453626</t>
+          <t>https://artportalen.se/Sighting/136453602</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136453627</v>
+        <v>136453637</v>
       </c>
       <c r="B19" t="n">
-        <v>93401</v>
+        <v>87501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2479,21 +2519,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>3690</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2503,10 +2543,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>688746</v>
+        <v>688710</v>
       </c>
       <c r="R19" t="n">
-        <v>7412678</v>
+        <v>7412627</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2564,16 +2604,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453627</t>
+          <t>https://artportalen.se/Sighting/136453637</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136320487</v>
+        <v>136453640</v>
       </c>
       <c r="B20" t="n">
-        <v>93403</v>
+        <v>87501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2581,52 +2621,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4362</v>
+        <v>3690</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>Soop</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>688612</v>
+        <v>688802</v>
       </c>
       <c r="R20" t="n">
-        <v>7412681</v>
+        <v>7412543</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2653,35 +2678,24 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:56</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
@@ -2692,16 +2706,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320487</t>
+          <t>https://artportalen.se/Sighting/136453640</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136453653</v>
+        <v>136320486</v>
       </c>
       <c r="B21" t="n">
-        <v>93403</v>
+        <v>93401</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,21 +2723,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2747,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>688484</v>
+        <v>688598</v>
       </c>
       <c r="R21" t="n">
-        <v>7412889</v>
+        <v>7412746</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2766,9 +2780,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2783,7 +2807,7 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
@@ -2794,16 +2818,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453653</t>
+          <t>https://artportalen.se/Sighting/136320486</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136453654</v>
+        <v>136453625</v>
       </c>
       <c r="B22" t="n">
-        <v>93403</v>
+        <v>93401</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2811,21 +2835,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2835,10 +2859,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>688755</v>
+        <v>688757</v>
       </c>
       <c r="R22" t="n">
-        <v>7412675</v>
+        <v>7413031</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2896,16 +2920,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453654</t>
+          <t>https://artportalen.se/Sighting/136453625</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136320479</v>
+        <v>136453626</v>
       </c>
       <c r="B23" t="n">
-        <v>93409</v>
+        <v>93401</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2913,21 +2937,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2937,10 +2961,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>688599</v>
+        <v>688732</v>
       </c>
       <c r="R23" t="n">
-        <v>7412694</v>
+        <v>7412730</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2970,19 +2994,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2997,7 +3011,7 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
@@ -3008,16 +3022,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320479</t>
+          <t>https://artportalen.se/Sighting/136453626</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136453646</v>
+        <v>136453627</v>
       </c>
       <c r="B24" t="n">
-        <v>93409</v>
+        <v>93401</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3025,21 +3039,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3049,10 +3063,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>688630</v>
+        <v>688746</v>
       </c>
       <c r="R24" t="n">
-        <v>7413081</v>
+        <v>7412678</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3110,16 +3124,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453646</t>
+          <t>https://artportalen.se/Sighting/136453627</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136453647</v>
+        <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93409</v>
+        <v>93401</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,37 +3141,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q25" t="n">
         <v>688683</v>
       </c>
       <c r="R25" t="n">
-        <v>7413083</v>
+        <v>7412859</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3184,9 +3198,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3201,27 +3225,27 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453647</t>
+          <t>https://artportalen.se/Sighting/136814460</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136453648</v>
+        <v>136320487</v>
       </c>
       <c r="B26" t="n">
-        <v>93409</v>
+        <v>93403</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3229,37 +3253,52 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>688769</v>
+        <v>688612</v>
       </c>
       <c r="R26" t="n">
-        <v>7412925</v>
+        <v>7412681</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3286,24 +3325,35 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3314,16 +3364,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453648</t>
+          <t>https://artportalen.se/Sighting/136320487</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136453649</v>
+        <v>136453653</v>
       </c>
       <c r="B27" t="n">
-        <v>93409</v>
+        <v>93403</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3331,21 +3381,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3355,10 +3405,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>688799</v>
+        <v>688484</v>
       </c>
       <c r="R27" t="n">
-        <v>7412688</v>
+        <v>7412889</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3416,16 +3466,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453649</t>
+          <t>https://artportalen.se/Sighting/136453653</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136453650</v>
+        <v>136453654</v>
       </c>
       <c r="B28" t="n">
-        <v>93409</v>
+        <v>93403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3433,21 +3483,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3457,10 +3507,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>688746</v>
+        <v>688755</v>
       </c>
       <c r="R28" t="n">
-        <v>7412670</v>
+        <v>7412675</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3518,16 +3568,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453650</t>
+          <t>https://artportalen.se/Sighting/136453654</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136453651</v>
+        <v>136814451</v>
       </c>
       <c r="B29" t="n">
-        <v>93409</v>
+        <v>93403</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3535,37 +3585,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>688743</v>
+        <v>688675</v>
       </c>
       <c r="R29" t="n">
-        <v>7412560</v>
+        <v>7412729</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3592,9 +3642,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3609,65 +3669,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453651</t>
+          <t>https://artportalen.se/Sighting/136814451</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136320475</v>
+        <v>136814452</v>
       </c>
       <c r="B30" t="n">
-        <v>93413</v>
+        <v>93403</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688611</v>
+        <v>688672</v>
       </c>
       <c r="R30" t="n">
-        <v>7412650</v>
+        <v>7412721</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3696,7 +3756,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3706,7 +3766,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3721,62 +3781,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320475</t>
+          <t>https://artportalen.se/Sighting/136814452</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136320484</v>
+        <v>136814454</v>
       </c>
       <c r="B31" t="n">
-        <v>93413</v>
+        <v>93403</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4365</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688632</v>
+        <v>688682</v>
       </c>
       <c r="R31" t="n">
-        <v>7412785</v>
+        <v>7412781</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3808,7 +3868,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3818,7 +3878,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3833,27 +3893,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320484</t>
+          <t>https://artportalen.se/Sighting/136814454</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136453604</v>
+        <v>136814459</v>
       </c>
       <c r="B32" t="n">
-        <v>93421</v>
+        <v>93403</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3861,37 +3921,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688416</v>
+        <v>688649</v>
       </c>
       <c r="R32" t="n">
-        <v>7412828</v>
+        <v>7412806</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3918,9 +3978,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3935,27 +4005,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453604</t>
+          <t>https://artportalen.se/Sighting/136814459</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136453606</v>
+        <v>136814461</v>
       </c>
       <c r="B33" t="n">
-        <v>93421</v>
+        <v>93403</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3963,34 +4033,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>688676</v>
+        <v>688794</v>
       </c>
       <c r="R33" t="n">
-        <v>7413050</v>
+        <v>7413016</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4020,9 +4090,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4037,27 +4117,27 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453606</t>
+          <t>https://artportalen.se/Sighting/136814461</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136453608</v>
+        <v>136814463</v>
       </c>
       <c r="B34" t="n">
-        <v>93421</v>
+        <v>93403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4065,37 +4145,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>688686</v>
+        <v>688692</v>
       </c>
       <c r="R34" t="n">
-        <v>7413083</v>
+        <v>7413080</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4122,9 +4202,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4139,27 +4229,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453608</t>
+          <t>https://artportalen.se/Sighting/136814463</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136453610</v>
+        <v>136814488</v>
       </c>
       <c r="B35" t="n">
-        <v>93421</v>
+        <v>93403</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4167,37 +4257,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>688805</v>
+        <v>688612</v>
       </c>
       <c r="R35" t="n">
-        <v>7412528</v>
+        <v>7412693</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4224,9 +4314,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4241,27 +4341,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453610</t>
+          <t>https://artportalen.se/Sighting/136814488</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136453589</v>
+        <v>136320479</v>
       </c>
       <c r="B36" t="n">
-        <v>93053</v>
+        <v>93409</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4269,21 +4369,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4293,10 +4393,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>688788</v>
+        <v>688599</v>
       </c>
       <c r="R36" t="n">
-        <v>7412652</v>
+        <v>7412694</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4326,9 +4426,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4343,7 +4453,7 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
@@ -4354,16 +4464,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453589</t>
+          <t>https://artportalen.se/Sighting/136320479</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136453631</v>
+        <v>136453646</v>
       </c>
       <c r="B37" t="n">
-        <v>90705</v>
+        <v>93409</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4371,21 +4481,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4395,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>688695</v>
+        <v>688630</v>
       </c>
       <c r="R37" t="n">
-        <v>7412638</v>
+        <v>7413081</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4439,7 +4549,6 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4457,16 +4566,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453631</t>
+          <t>https://artportalen.se/Sighting/136453646</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136453634</v>
+        <v>136453647</v>
       </c>
       <c r="B38" t="n">
-        <v>90705</v>
+        <v>93409</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4474,21 +4583,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4498,10 +4607,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>688382</v>
+        <v>688683</v>
       </c>
       <c r="R38" t="n">
-        <v>7412847</v>
+        <v>7413083</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4559,16 +4668,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453634</t>
+          <t>https://artportalen.se/Sighting/136453647</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136453635</v>
+        <v>136453648</v>
       </c>
       <c r="B39" t="n">
-        <v>90705</v>
+        <v>93409</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4576,21 +4685,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4600,10 +4709,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>688661</v>
+        <v>688769</v>
       </c>
       <c r="R39" t="n">
-        <v>7413082</v>
+        <v>7412925</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4661,16 +4770,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453635</t>
+          <t>https://artportalen.se/Sighting/136453648</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136453636</v>
+        <v>136453649</v>
       </c>
       <c r="B40" t="n">
-        <v>90705</v>
+        <v>93409</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4678,21 +4787,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4702,10 +4811,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>688788</v>
+        <v>688799</v>
       </c>
       <c r="R40" t="n">
-        <v>7412702</v>
+        <v>7412688</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4763,16 +4872,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453636</t>
+          <t>https://artportalen.se/Sighting/136453649</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136453592</v>
+        <v>136453650</v>
       </c>
       <c r="B41" t="n">
-        <v>93435</v>
+        <v>93409</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4780,21 +4889,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4804,10 +4913,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>688668</v>
+        <v>688746</v>
       </c>
       <c r="R41" t="n">
-        <v>7413059</v>
+        <v>7412670</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4865,38 +4974,38 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453592</t>
+          <t>https://artportalen.se/Sighting/136453650</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136320482</v>
+        <v>136453651</v>
       </c>
       <c r="B42" t="n">
-        <v>91465</v>
+        <v>93409</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4906,13 +5015,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>688676</v>
+        <v>688743</v>
       </c>
       <c r="R42" t="n">
-        <v>7412739</v>
+        <v>7412560</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4939,35 +5048,24 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
@@ -4978,54 +5076,54 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320482</t>
+          <t>https://artportalen.se/Sighting/136453651</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136320483</v>
+        <v>136814447</v>
       </c>
       <c r="B43" t="n">
-        <v>93393</v>
+        <v>93409</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>688686</v>
+        <v>688729</v>
       </c>
       <c r="R43" t="n">
-        <v>7412816</v>
+        <v>7412676</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5054,7 +5152,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5064,7 +5162,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5079,62 +5177,62 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320483</t>
+          <t>https://artportalen.se/Sighting/136814447</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136453628</v>
+        <v>136814458</v>
       </c>
       <c r="B44" t="n">
-        <v>79500</v>
+        <v>93409</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>688754</v>
+        <v>688672</v>
       </c>
       <c r="R44" t="n">
-        <v>7412697</v>
+        <v>7412830</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5164,9 +5262,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:37</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5181,27 +5289,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453628</t>
+          <t>https://artportalen.se/Sighting/136814458</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136453655</v>
+        <v>136814480</v>
       </c>
       <c r="B45" t="n">
-        <v>78879</v>
+        <v>93409</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5209,34 +5317,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>688481</v>
+        <v>688585</v>
       </c>
       <c r="R45" t="n">
-        <v>7412888</v>
+        <v>7412719</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5266,9 +5374,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5283,27 +5401,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453655</t>
+          <t>https://artportalen.se/Sighting/136814480</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136453656</v>
+        <v>136814486</v>
       </c>
       <c r="B46" t="n">
-        <v>78879</v>
+        <v>93409</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5311,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>688564</v>
+        <v>688599</v>
       </c>
       <c r="R46" t="n">
-        <v>7413072</v>
+        <v>7412701</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5368,9 +5486,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5385,49 +5513,49 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453656</t>
+          <t>https://artportalen.se/Sighting/136814486</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136453555</v>
+        <v>136320475</v>
       </c>
       <c r="B47" t="n">
-        <v>80095</v>
+        <v>93413</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>4365</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5437,13 +5565,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>688644</v>
+        <v>688611</v>
       </c>
       <c r="R47" t="n">
-        <v>7413032</v>
+        <v>7412650</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5470,9 +5598,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5487,7 +5625,7 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -5498,38 +5636,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453555</t>
+          <t>https://artportalen.se/Sighting/136320475</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136453629</v>
+        <v>136320484</v>
       </c>
       <c r="B48" t="n">
-        <v>80595</v>
+        <v>93413</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6461</v>
+        <v>4365</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5539,10 +5677,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>688689</v>
+        <v>688632</v>
       </c>
       <c r="R48" t="n">
-        <v>7413053</v>
+        <v>7412785</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5572,9 +5710,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5589,7 +5737,7 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
@@ -5600,58 +5748,54 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453629</t>
+          <t>https://artportalen.se/Sighting/136320484</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136453641</v>
+        <v>136814442</v>
       </c>
       <c r="B49" t="n">
-        <v>58112</v>
+        <v>93413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103031</v>
+        <v>4365</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>688728</v>
+        <v>688703</v>
       </c>
       <c r="R49" t="n">
-        <v>7412723</v>
+        <v>7412635</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5678,9 +5822,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5695,62 +5849,62 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453641</t>
+          <t>https://artportalen.se/Sighting/136814442</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136453616</v>
+        <v>136814481</v>
       </c>
       <c r="B50" t="n">
-        <v>98219</v>
+        <v>93413</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>688676</v>
+        <v>688584</v>
       </c>
       <c r="R50" t="n">
-        <v>7412815</v>
+        <v>7412718</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5780,9 +5934,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5797,49 +5961,49 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453616</t>
+          <t>https://artportalen.se/Sighting/136814481</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136453618</v>
+        <v>136453604</v>
       </c>
       <c r="B51" t="n">
-        <v>98219</v>
+        <v>93421</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5849,10 +6013,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>688794</v>
+        <v>688416</v>
       </c>
       <c r="R51" t="n">
-        <v>7412706</v>
+        <v>7412828</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -5910,38 +6074,38 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453618</t>
+          <t>https://artportalen.se/Sighting/136453604</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136453620</v>
+        <v>136453606</v>
       </c>
       <c r="B52" t="n">
-        <v>98219</v>
+        <v>93421</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5951,10 +6115,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>688698</v>
+        <v>688676</v>
       </c>
       <c r="R52" t="n">
-        <v>7412629</v>
+        <v>7413050</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6012,38 +6176,38 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453620</t>
+          <t>https://artportalen.se/Sighting/136453606</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136453622</v>
+        <v>136453608</v>
       </c>
       <c r="B53" t="n">
-        <v>98219</v>
+        <v>93421</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6053,10 +6217,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>688724</v>
+        <v>688686</v>
       </c>
       <c r="R53" t="n">
-        <v>7412621</v>
+        <v>7413083</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6114,38 +6278,38 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453622</t>
+          <t>https://artportalen.se/Sighting/136453608</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136453623</v>
+        <v>136453610</v>
       </c>
       <c r="B54" t="n">
-        <v>98219</v>
+        <v>93421</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6155,10 +6319,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>688725</v>
+        <v>688805</v>
       </c>
       <c r="R54" t="n">
-        <v>7412597</v>
+        <v>7412528</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6216,16 +6380,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453623</t>
+          <t>https://artportalen.se/Sighting/136453610</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136453575</v>
+        <v>136814468</v>
       </c>
       <c r="B55" t="n">
-        <v>79499</v>
+        <v>93421</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6233,34 +6397,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>260591</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>688561</v>
+        <v>688656</v>
       </c>
       <c r="R55" t="n">
-        <v>7413047</v>
+        <v>7413083</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6290,9 +6454,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6307,27 +6481,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453575</t>
+          <t>https://artportalen.se/Sighting/136814468</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136453577</v>
+        <v>136453589</v>
       </c>
       <c r="B56" t="n">
-        <v>79499</v>
+        <v>93053</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6335,21 +6509,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>260591</v>
+        <v>4745</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6359,10 +6533,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>688702</v>
+        <v>688788</v>
       </c>
       <c r="R56" t="n">
-        <v>7412735</v>
+        <v>7412652</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6420,16 +6594,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453577</t>
+          <t>https://artportalen.se/Sighting/136453589</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136453579</v>
+        <v>136453631</v>
       </c>
       <c r="B57" t="n">
-        <v>79499</v>
+        <v>90705</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6437,21 +6611,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>260591</v>
+        <v>4962</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6461,10 +6635,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>688781</v>
+        <v>688695</v>
       </c>
       <c r="R57" t="n">
-        <v>7412725</v>
+        <v>7412638</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6505,6 +6679,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6522,16 +6697,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453579</t>
+          <t>https://artportalen.se/Sighting/136453631</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136453581</v>
+        <v>136453634</v>
       </c>
       <c r="B58" t="n">
-        <v>79499</v>
+        <v>90705</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6539,21 +6714,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>260591</v>
+        <v>4962</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6563,10 +6738,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>688787</v>
+        <v>688382</v>
       </c>
       <c r="R58" t="n">
-        <v>7412707</v>
+        <v>7412847</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6624,16 +6799,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453581</t>
+          <t>https://artportalen.se/Sighting/136453634</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136453583</v>
+        <v>136453635</v>
       </c>
       <c r="B59" t="n">
-        <v>79499</v>
+        <v>90705</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6641,21 +6816,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>260591</v>
+        <v>4962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6665,10 +6840,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>688757</v>
+        <v>688661</v>
       </c>
       <c r="R59" t="n">
-        <v>7412706</v>
+        <v>7413082</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6726,16 +6901,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453583</t>
+          <t>https://artportalen.se/Sighting/136453635</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136453585</v>
+        <v>136453636</v>
       </c>
       <c r="B60" t="n">
-        <v>79499</v>
+        <v>90705</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6743,21 +6918,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>260591</v>
+        <v>4962</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6767,10 +6942,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>688699</v>
+        <v>688788</v>
       </c>
       <c r="R60" t="n">
-        <v>7412642</v>
+        <v>7412702</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -6828,16 +7003,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453585</t>
+          <t>https://artportalen.se/Sighting/136453636</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136453587</v>
+        <v>136453592</v>
       </c>
       <c r="B61" t="n">
-        <v>79499</v>
+        <v>93435</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6845,21 +7020,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>260591</v>
+        <v>5448</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6869,10 +7044,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>688715</v>
+        <v>688668</v>
       </c>
       <c r="R61" t="n">
-        <v>7412627</v>
+        <v>7413059</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -6930,7 +7105,4425 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136453592</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>136320482</v>
+      </c>
+      <c r="B62" t="n">
+        <v>91465</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>688676</v>
+      </c>
+      <c r="R62" t="n">
+        <v>7412739</v>
+      </c>
+      <c r="S62" t="n">
+        <v>7</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320482</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>136320483</v>
+      </c>
+      <c r="B63" t="n">
+        <v>93393</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>688686</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7412816</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Linnea Ingelsbo</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136320483</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>136814444</v>
+      </c>
+      <c r="B64" t="n">
+        <v>93393</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>688704</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7412632</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814444</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>136814473</v>
+      </c>
+      <c r="B65" t="n">
+        <v>90874</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>688528</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7412947</v>
+      </c>
+      <c r="S65" t="n">
+        <v>5</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814473</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>136814453</v>
+      </c>
+      <c r="B66" t="n">
+        <v>90893</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>688671</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7412721</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814453</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>136814456</v>
+      </c>
+      <c r="B67" t="n">
+        <v>90893</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>688687</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7412760</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814456</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>136814469</v>
+      </c>
+      <c r="B68" t="n">
+        <v>90893</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6286</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Torrmusseron</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Tricholoma sudum</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>688590</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7413075</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814469</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>136453628</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79500</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>688754</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7412697</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453628</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>136453655</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>688481</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7412888</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453655</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>136453656</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>688564</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7413072</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453656</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>136814474</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>688530</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7412946</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814474</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>136814478</v>
+      </c>
+      <c r="B73" t="n">
+        <v>78879</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>688614</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7412854</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814478</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>136814475</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79233</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>688543</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7412924</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814475</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>136453555</v>
+      </c>
+      <c r="B75" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>688644</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7413032</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453555</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>136814467</v>
+      </c>
+      <c r="B76" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>688654</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7413104</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814467</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>136814477</v>
+      </c>
+      <c r="B77" t="n">
+        <v>80095</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>688614</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7412854</v>
+      </c>
+      <c r="S77" t="n">
+        <v>5</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814477</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>136453629</v>
+      </c>
+      <c r="B78" t="n">
+        <v>80595</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>688689</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7413053</v>
+      </c>
+      <c r="S78" t="n">
+        <v>5</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453629</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>136814466</v>
+      </c>
+      <c r="B79" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>688654</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7413103</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814466</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>136453641</v>
+      </c>
+      <c r="B80" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>688728</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7412723</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453641</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>136814455</v>
+      </c>
+      <c r="B81" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>688685</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7412758</v>
+      </c>
+      <c r="S81" t="n">
+        <v>6</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814455</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>136453616</v>
+      </c>
+      <c r="B82" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>688676</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7412815</v>
+      </c>
+      <c r="S82" t="n">
+        <v>5</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453616</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>136453618</v>
+      </c>
+      <c r="B83" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>688794</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7412706</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453618</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>136453620</v>
+      </c>
+      <c r="B84" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>688698</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7412629</v>
+      </c>
+      <c r="S84" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453620</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>136453622</v>
+      </c>
+      <c r="B85" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>688724</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7412621</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453622</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>136453623</v>
+      </c>
+      <c r="B86" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>688725</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7412597</v>
+      </c>
+      <c r="S86" t="n">
+        <v>5</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453623</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>136814457</v>
+      </c>
+      <c r="B87" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>688687</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7412821</v>
+      </c>
+      <c r="S87" t="n">
+        <v>5</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814457</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>136814464</v>
+      </c>
+      <c r="B88" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>688651</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7413103</v>
+      </c>
+      <c r="S88" t="n">
+        <v>18</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814464</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>136814476</v>
+      </c>
+      <c r="B89" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>688618</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7412849</v>
+      </c>
+      <c r="S89" t="n">
+        <v>5</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814476</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>136814485</v>
+      </c>
+      <c r="B90" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>688579</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7412740</v>
+      </c>
+      <c r="S90" t="n">
+        <v>7</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814485</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>136814487</v>
+      </c>
+      <c r="B91" t="n">
+        <v>80066</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>688615</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7412698</v>
+      </c>
+      <c r="S91" t="n">
+        <v>6</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814487</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>136814482</v>
+      </c>
+      <c r="B92" t="n">
+        <v>93440</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7412723</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814482</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>136453575</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>688561</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7413047</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453575</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>136453577</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>688702</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7412735</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453577</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>136453579</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>688781</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7412725</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453579</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>136453581</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>688787</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7412707</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453581</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>136453583</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>688757</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7412706</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453583</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>136453585</v>
+      </c>
+      <c r="B98" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>688699</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7412642</v>
+      </c>
+      <c r="S98" t="n">
+        <v>5</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136453585</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>136453587</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Várditjåhkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>688715</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7412627</v>
+      </c>
+      <c r="S99" t="n">
+        <v>5</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136453587</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>136814446</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>688717</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7412657</v>
+      </c>
+      <c r="S100" t="n">
+        <v>5</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814446</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>136814472</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>688530</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7412959</v>
+      </c>
+      <c r="S101" t="n">
+        <v>5</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814472</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>136814479</v>
+      </c>
+      <c r="B102" t="n">
+        <v>93430</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7412719</v>
+      </c>
+      <c r="S102" t="n">
+        <v>5</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr"/>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814479</t>
         </is>
       </c>
     </row>
@@ -6996,6 +11589,47 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ102"/>
+  <dimension ref="A1:AZ104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1243,7 +1243,7 @@
         <v>136320478</v>
       </c>
       <c r="B7" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136453642</v>
       </c>
       <c r="B8" t="n">
-        <v>92290</v>
+        <v>92292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91115</v>
+        <v>91117</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136453551</v>
       </c>
       <c r="B12" t="n">
-        <v>92033</v>
+        <v>92035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>136453553</v>
       </c>
       <c r="B13" t="n">
-        <v>92033</v>
+        <v>92035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136453594</v>
       </c>
       <c r="B14" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136453596</v>
       </c>
       <c r="B15" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>136453598</v>
       </c>
       <c r="B16" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136453600</v>
       </c>
       <c r="B17" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136453602</v>
       </c>
       <c r="B18" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>136453637</v>
       </c>
       <c r="B19" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>136453640</v>
       </c>
       <c r="B20" t="n">
-        <v>87501</v>
+        <v>87503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>136320486</v>
       </c>
       <c r="B21" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>136453625</v>
       </c>
       <c r="B22" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136453626</v>
       </c>
       <c r="B23" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136453627</v>
       </c>
       <c r="B24" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>136320487</v>
       </c>
       <c r="B26" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>136453653</v>
       </c>
       <c r="B27" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136453654</v>
       </c>
       <c r="B28" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>136814451</v>
       </c>
       <c r="B29" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>136814452</v>
       </c>
       <c r="B30" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>136814454</v>
       </c>
       <c r="B31" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>136814459</v>
       </c>
       <c r="B32" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136814461</v>
       </c>
       <c r="B33" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>136814463</v>
       </c>
       <c r="B34" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>136814488</v>
       </c>
       <c r="B35" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>136320479</v>
       </c>
       <c r="B36" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>136453646</v>
       </c>
       <c r="B37" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>136453647</v>
       </c>
       <c r="B38" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>136453648</v>
       </c>
       <c r="B39" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136453649</v>
       </c>
       <c r="B40" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136453650</v>
       </c>
       <c r="B41" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>136453651</v>
       </c>
       <c r="B42" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>136814447</v>
       </c>
       <c r="B43" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>136814458</v>
       </c>
       <c r="B44" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>136814480</v>
       </c>
       <c r="B45" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>136814486</v>
       </c>
       <c r="B46" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>136320475</v>
       </c>
       <c r="B47" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>136320484</v>
       </c>
       <c r="B48" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>136814442</v>
       </c>
       <c r="B49" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>136814481</v>
       </c>
       <c r="B50" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136453604</v>
       </c>
       <c r="B51" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>136453606</v>
       </c>
       <c r="B52" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>136453608</v>
       </c>
       <c r="B53" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>136453610</v>
       </c>
       <c r="B54" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>136814468</v>
       </c>
       <c r="B55" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136453589</v>
       </c>
       <c r="B56" t="n">
-        <v>93053</v>
+        <v>93055</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>136453631</v>
       </c>
       <c r="B57" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>136453634</v>
       </c>
       <c r="B58" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>136453635</v>
       </c>
       <c r="B59" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136453636</v>
       </c>
       <c r="B60" t="n">
-        <v>90705</v>
+        <v>90707</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>136453592</v>
       </c>
       <c r="B61" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>136320482</v>
       </c>
       <c r="B62" t="n">
-        <v>91465</v>
+        <v>91467</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>136320483</v>
       </c>
       <c r="B63" t="n">
-        <v>93393</v>
+        <v>93395</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>136814444</v>
       </c>
       <c r="B64" t="n">
-        <v>93393</v>
+        <v>93395</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>136814473</v>
       </c>
       <c r="B65" t="n">
-        <v>90874</v>
+        <v>90876</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7560,10 +7560,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136814453</v>
+        <v>136453557</v>
       </c>
       <c r="B66" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7588,17 +7588,24 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr"/>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>688671</v>
+        <v>688707</v>
       </c>
       <c r="R66" t="n">
-        <v>7412721</v>
+        <v>7412748</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7628,54 +7635,45 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814453</t>
+          <t>https://artportalen.se/Sighting/136453557</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136814456</v>
+        <v>136453561</v>
       </c>
       <c r="B67" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7700,17 +7698,28 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>688687</v>
+        <v>688727</v>
       </c>
       <c r="R67" t="n">
-        <v>7412760</v>
+        <v>7412612</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7740,54 +7749,45 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814456</t>
+          <t>https://artportalen.se/Sighting/136453561</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136814469</v>
+        <v>136814453</v>
       </c>
       <c r="B68" t="n">
-        <v>90893</v>
+        <v>90895</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7819,10 +7819,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>688590</v>
+        <v>688671</v>
       </c>
       <c r="R68" t="n">
-        <v>7413075</v>
+        <v>7412721</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7890,51 +7890,51 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814469</t>
+          <t>https://artportalen.se/Sighting/136814453</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136453628</v>
+        <v>136814456</v>
       </c>
       <c r="B69" t="n">
-        <v>79500</v>
+        <v>90895</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>688754</v>
+        <v>688687</v>
       </c>
       <c r="R69" t="n">
-        <v>7412697</v>
+        <v>7412760</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7964,9 +7964,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7981,62 +7991,62 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453628</t>
+          <t>https://artportalen.se/Sighting/136814456</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136453655</v>
+        <v>136814469</v>
       </c>
       <c r="B70" t="n">
-        <v>78879</v>
+        <v>90895</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6437</v>
+        <v>6286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>688481</v>
+        <v>688590</v>
       </c>
       <c r="R70" t="n">
-        <v>7412888</v>
+        <v>7413075</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8066,9 +8076,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8083,49 +8103,49 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453655</t>
+          <t>https://artportalen.se/Sighting/136814469</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136453656</v>
+        <v>136453628</v>
       </c>
       <c r="B71" t="n">
-        <v>78879</v>
+        <v>79500</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8135,10 +8155,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>688564</v>
+        <v>688754</v>
       </c>
       <c r="R71" t="n">
-        <v>7413072</v>
+        <v>7412697</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8196,13 +8216,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453656</t>
+          <t>https://artportalen.se/Sighting/136453628</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136814474</v>
+        <v>136453655</v>
       </c>
       <c r="B72" t="n">
         <v>78879</v>
@@ -8233,14 +8253,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688530</v>
+        <v>688481</v>
       </c>
       <c r="R72" t="n">
-        <v>7412946</v>
+        <v>7412888</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8270,19 +8290,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8297,24 +8307,24 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814474</t>
+          <t>https://artportalen.se/Sighting/136453655</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136814478</v>
+        <v>136453656</v>
       </c>
       <c r="B73" t="n">
         <v>78879</v>
@@ -8345,14 +8355,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688614</v>
+        <v>688564</v>
       </c>
       <c r="R73" t="n">
-        <v>7412854</v>
+        <v>7413072</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8382,19 +8392,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8409,27 +8409,27 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814478</t>
+          <t>https://artportalen.se/Sighting/136453656</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136814475</v>
+        <v>136814474</v>
       </c>
       <c r="B74" t="n">
-        <v>79233</v>
+        <v>78879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8437,21 +8437,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8461,10 +8461,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688543</v>
+        <v>688530</v>
       </c>
       <c r="R74" t="n">
-        <v>7412924</v>
+        <v>7412946</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8532,16 +8532,16 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814475</t>
+          <t>https://artportalen.se/Sighting/136814474</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136453555</v>
+        <v>136814478</v>
       </c>
       <c r="B75" t="n">
-        <v>80095</v>
+        <v>78879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8549,34 +8549,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688644</v>
+        <v>688614</v>
       </c>
       <c r="R75" t="n">
-        <v>7413032</v>
+        <v>7412854</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8606,9 +8606,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8623,27 +8633,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453555</t>
+          <t>https://artportalen.se/Sighting/136814478</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136814467</v>
+        <v>136814475</v>
       </c>
       <c r="B76" t="n">
-        <v>80095</v>
+        <v>79233</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8651,21 +8661,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8675,10 +8685,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>688654</v>
+        <v>688543</v>
       </c>
       <c r="R76" t="n">
-        <v>7413104</v>
+        <v>7412924</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8710,7 +8720,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8720,7 +8730,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8746,13 +8756,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814467</t>
+          <t>https://artportalen.se/Sighting/136814475</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136814477</v>
+        <v>136453555</v>
       </c>
       <c r="B77" t="n">
         <v>80095</v>
@@ -8783,14 +8793,14 @@
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>688614</v>
+        <v>688644</v>
       </c>
       <c r="R77" t="n">
-        <v>7412854</v>
+        <v>7413032</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8820,19 +8830,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8847,62 +8847,62 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814477</t>
+          <t>https://artportalen.se/Sighting/136453555</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136453629</v>
+        <v>136814467</v>
       </c>
       <c r="B78" t="n">
-        <v>80595</v>
+        <v>80095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>688689</v>
+        <v>688654</v>
       </c>
       <c r="R78" t="n">
-        <v>7413053</v>
+        <v>7413104</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8932,9 +8932,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8949,27 +8959,27 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453629</t>
+          <t>https://artportalen.se/Sighting/136814467</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136814466</v>
+        <v>136814477</v>
       </c>
       <c r="B79" t="n">
-        <v>58169</v>
+        <v>80095</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8977,21 +8987,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9001,10 +9011,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>688654</v>
+        <v>688614</v>
       </c>
       <c r="R79" t="n">
-        <v>7413103</v>
+        <v>7412854</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9036,7 +9046,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9046,7 +9056,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9072,55 +9082,51 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814466</t>
+          <t>https://artportalen.se/Sighting/136814477</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136453641</v>
+        <v>136453629</v>
       </c>
       <c r="B80" t="n">
-        <v>58112</v>
+        <v>80595</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>688728</v>
+        <v>688689</v>
       </c>
       <c r="R80" t="n">
-        <v>7412723</v>
+        <v>7413053</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9178,16 +9184,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453641</t>
+          <t>https://artportalen.se/Sighting/136453629</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136814455</v>
+        <v>136814466</v>
       </c>
       <c r="B81" t="n">
-        <v>58112</v>
+        <v>58169</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9195,21 +9201,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9219,13 +9225,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>688685</v>
+        <v>688654</v>
       </c>
       <c r="R81" t="n">
-        <v>7412758</v>
+        <v>7413103</v>
       </c>
       <c r="S81" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9254,7 +9260,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9264,7 +9270,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9290,51 +9296,55 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814455</t>
+          <t>https://artportalen.se/Sighting/136814466</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136453616</v>
+        <v>136453641</v>
       </c>
       <c r="B82" t="n">
-        <v>98219</v>
+        <v>58112</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>688676</v>
+        <v>688728</v>
       </c>
       <c r="R82" t="n">
-        <v>7412815</v>
+        <v>7412723</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9392,54 +9402,54 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453616</t>
+          <t>https://artportalen.se/Sighting/136453641</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136453618</v>
+        <v>136814455</v>
       </c>
       <c r="B83" t="n">
-        <v>98219</v>
+        <v>58112</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>688794</v>
+        <v>688685</v>
       </c>
       <c r="R83" t="n">
-        <v>7412706</v>
+        <v>7412758</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9466,9 +9476,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9483,27 +9503,27 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453618</t>
+          <t>https://artportalen.se/Sighting/136814455</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136453620</v>
+        <v>136453616</v>
       </c>
       <c r="B84" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9535,10 +9555,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688698</v>
+        <v>688676</v>
       </c>
       <c r="R84" t="n">
-        <v>7412629</v>
+        <v>7412815</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9596,16 +9616,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453620</t>
+          <t>https://artportalen.se/Sighting/136453616</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136453622</v>
+        <v>136453618</v>
       </c>
       <c r="B85" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9637,10 +9657,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688724</v>
+        <v>688794</v>
       </c>
       <c r="R85" t="n">
-        <v>7412621</v>
+        <v>7412706</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -9698,16 +9718,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453622</t>
+          <t>https://artportalen.se/Sighting/136453618</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136453623</v>
+        <v>136453620</v>
       </c>
       <c r="B86" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9739,10 +9759,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688725</v>
+        <v>688698</v>
       </c>
       <c r="R86" t="n">
-        <v>7412597</v>
+        <v>7412629</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9800,16 +9820,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453623</t>
+          <t>https://artportalen.se/Sighting/136453620</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136814457</v>
+        <v>136453622</v>
       </c>
       <c r="B87" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9837,14 +9857,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>688687</v>
+        <v>688724</v>
       </c>
       <c r="R87" t="n">
-        <v>7412821</v>
+        <v>7412621</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9874,19 +9894,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>11:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9901,65 +9911,65 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814457</t>
+          <t>https://artportalen.se/Sighting/136453622</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136814464</v>
+        <v>136453623</v>
       </c>
       <c r="B88" t="n">
-        <v>80066</v>
+        <v>98221</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>688651</v>
+        <v>688725</v>
       </c>
       <c r="R88" t="n">
-        <v>7413103</v>
+        <v>7412597</v>
       </c>
       <c r="S88" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9986,19 +9996,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10013,49 +10013,49 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814464</t>
+          <t>https://artportalen.se/Sighting/136453623</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136814476</v>
+        <v>136814457</v>
       </c>
       <c r="B89" t="n">
-        <v>80066</v>
+        <v>98221</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10065,10 +10065,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>688618</v>
+        <v>688687</v>
       </c>
       <c r="R89" t="n">
-        <v>7412849</v>
+        <v>7412821</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10110,7 +10110,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10136,13 +10136,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814476</t>
+          <t>https://artportalen.se/Sighting/136814457</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136814485</v>
+        <v>136814464</v>
       </c>
       <c r="B90" t="n">
         <v>80066</v>
@@ -10177,13 +10177,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>688579</v>
+        <v>688651</v>
       </c>
       <c r="R90" t="n">
-        <v>7412740</v>
+        <v>7413103</v>
       </c>
       <c r="S90" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10212,7 +10212,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10222,7 +10222,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10248,13 +10248,13 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814485</t>
+          <t>https://artportalen.se/Sighting/136814464</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136814487</v>
+        <v>136814476</v>
       </c>
       <c r="B91" t="n">
         <v>80066</v>
@@ -10289,13 +10289,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>688615</v>
+        <v>688618</v>
       </c>
       <c r="R91" t="n">
-        <v>7412698</v>
+        <v>7412849</v>
       </c>
       <c r="S91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10324,7 +10324,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10334,7 +10334,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10360,38 +10360,38 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814487</t>
+          <t>https://artportalen.se/Sighting/136814476</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136814482</v>
+        <v>136814485</v>
       </c>
       <c r="B92" t="n">
-        <v>93440</v>
+        <v>80066</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10401,13 +10401,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>688585</v>
+        <v>688579</v>
       </c>
       <c r="R92" t="n">
-        <v>7412723</v>
+        <v>7412740</v>
       </c>
       <c r="S92" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10472,16 +10472,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814482</t>
+          <t>https://artportalen.se/Sighting/136814485</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136453575</v>
+        <v>136814487</v>
       </c>
       <c r="B93" t="n">
-        <v>79499</v>
+        <v>80066</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10489,37 +10489,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>688561</v>
+        <v>688615</v>
       </c>
       <c r="R93" t="n">
-        <v>7413047</v>
+        <v>7412698</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10546,9 +10546,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10563,62 +10573,62 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453575</t>
+          <t>https://artportalen.se/Sighting/136814487</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136453577</v>
+        <v>136814482</v>
       </c>
       <c r="B94" t="n">
-        <v>79499</v>
+        <v>93442</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>260591</v>
+        <v>232140</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>688702</v>
+        <v>688585</v>
       </c>
       <c r="R94" t="n">
-        <v>7412735</v>
+        <v>7412723</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -10648,9 +10658,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10665,24 +10685,24 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453577</t>
+          <t>https://artportalen.se/Sighting/136814482</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>136453579</v>
+        <v>136453575</v>
       </c>
       <c r="B95" t="n">
         <v>79499</v>
@@ -10717,10 +10737,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>688781</v>
+        <v>688561</v>
       </c>
       <c r="R95" t="n">
-        <v>7412725</v>
+        <v>7413047</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -10778,13 +10798,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453579</t>
+          <t>https://artportalen.se/Sighting/136453575</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>136453581</v>
+        <v>136453577</v>
       </c>
       <c r="B96" t="n">
         <v>79499</v>
@@ -10819,10 +10839,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>688787</v>
+        <v>688702</v>
       </c>
       <c r="R96" t="n">
-        <v>7412707</v>
+        <v>7412735</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10880,13 +10900,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453581</t>
+          <t>https://artportalen.se/Sighting/136453577</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>136453583</v>
+        <v>136453579</v>
       </c>
       <c r="B97" t="n">
         <v>79499</v>
@@ -10921,10 +10941,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>688757</v>
+        <v>688781</v>
       </c>
       <c r="R97" t="n">
-        <v>7412706</v>
+        <v>7412725</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -10982,13 +11002,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453583</t>
+          <t>https://artportalen.se/Sighting/136453579</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>136453585</v>
+        <v>136453581</v>
       </c>
       <c r="B98" t="n">
         <v>79499</v>
@@ -11023,10 +11043,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>688699</v>
+        <v>688787</v>
       </c>
       <c r="R98" t="n">
-        <v>7412642</v>
+        <v>7412707</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11084,13 +11104,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453585</t>
+          <t>https://artportalen.se/Sighting/136453581</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>136453587</v>
+        <v>136453583</v>
       </c>
       <c r="B99" t="n">
         <v>79499</v>
@@ -11125,10 +11145,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>688715</v>
+        <v>688757</v>
       </c>
       <c r="R99" t="n">
-        <v>7412627</v>
+        <v>7412706</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11186,13 +11206,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453587</t>
+          <t>https://artportalen.se/Sighting/136453583</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136814446</v>
+        <v>136453585</v>
       </c>
       <c r="B100" t="n">
         <v>79499</v>
@@ -11223,14 +11243,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>688717</v>
+        <v>688699</v>
       </c>
       <c r="R100" t="n">
-        <v>7412657</v>
+        <v>7412642</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11260,19 +11280,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11287,24 +11297,24 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814446</t>
+          <t>https://artportalen.se/Sighting/136453585</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>136814472</v>
+        <v>136453587</v>
       </c>
       <c r="B101" t="n">
         <v>79499</v>
@@ -11335,14 +11345,14 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>688530</v>
+        <v>688715</v>
       </c>
       <c r="R101" t="n">
-        <v>7412959</v>
+        <v>7412627</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11372,19 +11382,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11399,27 +11399,27 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814472</t>
+          <t>https://artportalen.se/Sighting/136453587</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136814479</v>
+        <v>136814446</v>
       </c>
       <c r="B102" t="n">
-        <v>93430</v>
+        <v>79499</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11427,21 +11427,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6331648</v>
+        <v>260591</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Nordtaggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11451,10 +11451,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>688585</v>
+        <v>688717</v>
       </c>
       <c r="R102" t="n">
-        <v>7412719</v>
+        <v>7412657</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11486,7 +11486,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11505,7 +11505,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11522,6 +11521,231 @@
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814446</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>136814472</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>688530</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7412959</v>
+      </c>
+      <c r="S103" t="n">
+        <v>5</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814472</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>136814479</v>
+      </c>
+      <c r="B104" t="n">
+        <v>93432</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7412719</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136814479</t>
         </is>
@@ -11630,6 +11854,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136320476</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136320480</v>
       </c>
       <c r="B3" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136320481</v>
       </c>
       <c r="B4" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136320478</v>
       </c>
       <c r="B7" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136453642</v>
       </c>
       <c r="B8" t="n">
-        <v>92292</v>
+        <v>92294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91117</v>
+        <v>91119</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93436</v>
+        <v>93438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136453551</v>
       </c>
       <c r="B12" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>136453553</v>
       </c>
       <c r="B13" t="n">
-        <v>92035</v>
+        <v>92037</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136453594</v>
       </c>
       <c r="B14" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136453596</v>
       </c>
       <c r="B15" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>136453598</v>
       </c>
       <c r="B16" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136453600</v>
       </c>
       <c r="B17" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136453602</v>
       </c>
       <c r="B18" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>136453637</v>
       </c>
       <c r="B19" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>136453640</v>
       </c>
       <c r="B20" t="n">
-        <v>87503</v>
+        <v>87505</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>136320486</v>
       </c>
       <c r="B21" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>136453625</v>
       </c>
       <c r="B22" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136453626</v>
       </c>
       <c r="B23" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136453627</v>
       </c>
       <c r="B24" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>136320487</v>
       </c>
       <c r="B26" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>136453653</v>
       </c>
       <c r="B27" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136453654</v>
       </c>
       <c r="B28" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>136814451</v>
       </c>
       <c r="B29" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>136814452</v>
       </c>
       <c r="B30" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>136814454</v>
       </c>
       <c r="B31" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>136814459</v>
       </c>
       <c r="B32" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136814461</v>
       </c>
       <c r="B33" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>136814463</v>
       </c>
       <c r="B34" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>136814488</v>
       </c>
       <c r="B35" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>136320479</v>
       </c>
       <c r="B36" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>136453646</v>
       </c>
       <c r="B37" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>136453647</v>
       </c>
       <c r="B38" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>136453648</v>
       </c>
       <c r="B39" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136453649</v>
       </c>
       <c r="B40" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136453650</v>
       </c>
       <c r="B41" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>136453651</v>
       </c>
       <c r="B42" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>136814447</v>
       </c>
       <c r="B43" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>136814458</v>
       </c>
       <c r="B44" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>136814480</v>
       </c>
       <c r="B45" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>136814486</v>
       </c>
       <c r="B46" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>136320475</v>
       </c>
       <c r="B47" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>136320484</v>
       </c>
       <c r="B48" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>136814442</v>
       </c>
       <c r="B49" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>136814481</v>
       </c>
       <c r="B50" t="n">
-        <v>93415</v>
+        <v>93417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136453604</v>
       </c>
       <c r="B51" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>136453606</v>
       </c>
       <c r="B52" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>136453608</v>
       </c>
       <c r="B53" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>136453610</v>
       </c>
       <c r="B54" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>136814468</v>
       </c>
       <c r="B55" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136453589</v>
       </c>
       <c r="B56" t="n">
-        <v>93055</v>
+        <v>93057</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>136453631</v>
       </c>
       <c r="B57" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>136453634</v>
       </c>
       <c r="B58" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>136453635</v>
       </c>
       <c r="B59" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136453636</v>
       </c>
       <c r="B60" t="n">
-        <v>90707</v>
+        <v>90709</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>136453592</v>
       </c>
       <c r="B61" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         <v>136320482</v>
       </c>
       <c r="B62" t="n">
-        <v>91467</v>
+        <v>91469</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>136320483</v>
       </c>
       <c r="B63" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>136814444</v>
       </c>
       <c r="B64" t="n">
-        <v>93395</v>
+        <v>93397</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>136814473</v>
       </c>
       <c r="B65" t="n">
-        <v>90876</v>
+        <v>90878</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136453557</v>
       </c>
       <c r="B66" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136453561</v>
       </c>
       <c r="B67" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136814453</v>
       </c>
       <c r="B68" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136814456</v>
       </c>
       <c r="B69" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>136814469</v>
       </c>
       <c r="B70" t="n">
-        <v>90895</v>
+        <v>90897</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>136453628</v>
       </c>
       <c r="B71" t="n">
-        <v>79500</v>
+        <v>79504</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>136453655</v>
       </c>
       <c r="B72" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>136453656</v>
       </c>
       <c r="B73" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>136814474</v>
       </c>
       <c r="B74" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>136814478</v>
       </c>
       <c r="B75" t="n">
-        <v>78879</v>
+        <v>78883</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>136814475</v>
       </c>
       <c r="B76" t="n">
-        <v>79233</v>
+        <v>79237</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>136453555</v>
       </c>
       <c r="B77" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136814467</v>
       </c>
       <c r="B78" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>136814477</v>
       </c>
       <c r="B79" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>136453629</v>
       </c>
       <c r="B80" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>136453616</v>
       </c>
       <c r="B84" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>136453618</v>
       </c>
       <c r="B85" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>136453620</v>
       </c>
       <c r="B86" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>136453622</v>
       </c>
       <c r="B87" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>136453623</v>
       </c>
       <c r="B88" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>136814457</v>
       </c>
       <c r="B89" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>136814464</v>
       </c>
       <c r="B90" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>136814476</v>
       </c>
       <c r="B91" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>136814485</v>
       </c>
       <c r="B92" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>136814487</v>
       </c>
       <c r="B93" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>136814482</v>
       </c>
       <c r="B94" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136453575</v>
       </c>
       <c r="B95" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136453577</v>
       </c>
       <c r="B96" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136453579</v>
       </c>
       <c r="B97" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>136453581</v>
       </c>
       <c r="B98" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>136453583</v>
       </c>
       <c r="B99" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>136453585</v>
       </c>
       <c r="B100" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>136453587</v>
       </c>
       <c r="B101" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>136814446</v>
       </c>
       <c r="B102" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>136814472</v>
       </c>
       <c r="B103" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>136814479</v>
       </c>
       <c r="B104" t="n">
-        <v>93432</v>
+        <v>93434</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136453642</v>
       </c>
       <c r="B8" t="n">
-        <v>92294</v>
+        <v>92296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91119</v>
+        <v>91121</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136453551</v>
       </c>
       <c r="B12" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>136453553</v>
       </c>
       <c r="B13" t="n">
-        <v>92037</v>
+        <v>92039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136453594</v>
       </c>
       <c r="B14" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136453596</v>
       </c>
       <c r="B15" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>136453598</v>
       </c>
       <c r="B16" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136453600</v>
       </c>
       <c r="B17" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136453602</v>
       </c>
       <c r="B18" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>136453637</v>
       </c>
       <c r="B19" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>136453640</v>
       </c>
       <c r="B20" t="n">
-        <v>87505</v>
+        <v>87507</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>136453625</v>
       </c>
       <c r="B22" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136453626</v>
       </c>
       <c r="B23" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136453627</v>
       </c>
       <c r="B24" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3373,7 +3373,7 @@
         <v>136453653</v>
       </c>
       <c r="B27" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3475,7 +3475,7 @@
         <v>136453654</v>
       </c>
       <c r="B28" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>136814451</v>
       </c>
       <c r="B29" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>136814452</v>
       </c>
       <c r="B30" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3801,7 +3801,7 @@
         <v>136814454</v>
       </c>
       <c r="B31" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3913,7 +3913,7 @@
         <v>136814459</v>
       </c>
       <c r="B32" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136814461</v>
       </c>
       <c r="B33" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4137,7 +4137,7 @@
         <v>136814463</v>
       </c>
       <c r="B34" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4249,7 +4249,7 @@
         <v>136814488</v>
       </c>
       <c r="B35" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4473,7 +4473,7 @@
         <v>136453646</v>
       </c>
       <c r="B37" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>136453647</v>
       </c>
       <c r="B38" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4677,7 +4677,7 @@
         <v>136453648</v>
       </c>
       <c r="B39" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>136453649</v>
       </c>
       <c r="B40" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>136453650</v>
       </c>
       <c r="B41" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>136453651</v>
       </c>
       <c r="B42" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>136814447</v>
       </c>
       <c r="B43" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>136814458</v>
       </c>
       <c r="B44" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5309,7 +5309,7 @@
         <v>136814480</v>
       </c>
       <c r="B45" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>136814486</v>
       </c>
       <c r="B46" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>136814442</v>
       </c>
       <c r="B49" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>136814481</v>
       </c>
       <c r="B50" t="n">
-        <v>93417</v>
+        <v>93419</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>136453604</v>
       </c>
       <c r="B51" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6083,7 +6083,7 @@
         <v>136453606</v>
       </c>
       <c r="B52" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6185,7 +6185,7 @@
         <v>136453608</v>
       </c>
       <c r="B53" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>136453610</v>
       </c>
       <c r="B54" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6389,7 +6389,7 @@
         <v>136814468</v>
       </c>
       <c r="B55" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,7 +6501,7 @@
         <v>136453589</v>
       </c>
       <c r="B56" t="n">
-        <v>93057</v>
+        <v>93059</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>136453631</v>
       </c>
       <c r="B57" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
         <v>136453634</v>
       </c>
       <c r="B58" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         <v>136453635</v>
       </c>
       <c r="B59" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>136453636</v>
       </c>
       <c r="B60" t="n">
-        <v>90709</v>
+        <v>90711</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7012,7 +7012,7 @@
         <v>136453592</v>
       </c>
       <c r="B61" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>136814444</v>
       </c>
       <c r="B64" t="n">
-        <v>93397</v>
+        <v>93399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>136814473</v>
       </c>
       <c r="B65" t="n">
-        <v>90878</v>
+        <v>90880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>136453557</v>
       </c>
       <c r="B66" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7673,7 +7673,7 @@
         <v>136453561</v>
       </c>
       <c r="B67" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136814453</v>
       </c>
       <c r="B68" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7899,7 +7899,7 @@
         <v>136814456</v>
       </c>
       <c r="B69" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>136814469</v>
       </c>
       <c r="B70" t="n">
-        <v>90897</v>
+        <v>90899</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8123,7 +8123,7 @@
         <v>136453628</v>
       </c>
       <c r="B71" t="n">
-        <v>79504</v>
+        <v>79506</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>136453655</v>
       </c>
       <c r="B72" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8327,7 +8327,7 @@
         <v>136453656</v>
       </c>
       <c r="B73" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>136814474</v>
       </c>
       <c r="B74" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         <v>136814478</v>
       </c>
       <c r="B75" t="n">
-        <v>78883</v>
+        <v>78885</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>136814475</v>
       </c>
       <c r="B76" t="n">
-        <v>79237</v>
+        <v>79239</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8765,7 +8765,7 @@
         <v>136453555</v>
       </c>
       <c r="B77" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8867,7 +8867,7 @@
         <v>136814467</v>
       </c>
       <c r="B78" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>136814477</v>
       </c>
       <c r="B79" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
         <v>136453629</v>
       </c>
       <c r="B80" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>136453616</v>
       </c>
       <c r="B84" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>136453618</v>
       </c>
       <c r="B85" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9727,7 +9727,7 @@
         <v>136453620</v>
       </c>
       <c r="B86" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>136453622</v>
       </c>
       <c r="B87" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>136453623</v>
       </c>
       <c r="B88" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10033,7 +10033,7 @@
         <v>136814457</v>
       </c>
       <c r="B89" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>136814464</v>
       </c>
       <c r="B90" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>136814476</v>
       </c>
       <c r="B91" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>136814485</v>
       </c>
       <c r="B92" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10481,7 +10481,7 @@
         <v>136814487</v>
       </c>
       <c r="B93" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>136814482</v>
       </c>
       <c r="B94" t="n">
-        <v>93444</v>
+        <v>93446</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>136453575</v>
       </c>
       <c r="B95" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>136453577</v>
       </c>
       <c r="B96" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10909,7 +10909,7 @@
         <v>136453579</v>
       </c>
       <c r="B97" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>136453581</v>
       </c>
       <c r="B98" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>136453583</v>
       </c>
       <c r="B99" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11215,7 +11215,7 @@
         <v>136453585</v>
       </c>
       <c r="B100" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11317,7 +11317,7 @@
         <v>136453587</v>
       </c>
       <c r="B101" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>136814446</v>
       </c>
       <c r="B102" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11531,7 +11531,7 @@
         <v>136814472</v>
       </c>
       <c r="B103" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11643,7 +11643,7 @@
         <v>136814479</v>
       </c>
       <c r="B104" t="n">
-        <v>93434</v>
+        <v>93436</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ104"/>
+  <dimension ref="A1:AZ106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>136453642</v>
       </c>
       <c r="B8" t="n">
-        <v>92296</v>
+        <v>92297</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93440</v>
+        <v>93441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136453551</v>
       </c>
       <c r="B12" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>136453553</v>
       </c>
       <c r="B13" t="n">
-        <v>92039</v>
+        <v>92040</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136453594</v>
       </c>
       <c r="B14" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136453596</v>
       </c>
       <c r="B15" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>136453598</v>
       </c>
       <c r="B16" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136453600</v>
       </c>
       <c r="B17" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136453602</v>
       </c>
       <c r="B18" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>136453637</v>
       </c>
       <c r="B19" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>136453640</v>
       </c>
       <c r="B20" t="n">
-        <v>87507</v>
+        <v>87508</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>136453625</v>
       </c>
       <c r="B22" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136453626</v>
       </c>
       <c r="B23" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136453627</v>
       </c>
       <c r="B24" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3242,10 +3242,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136320487</v>
+        <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93407</v>
+        <v>93408</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3253,33 +3253,29 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>teleomorf</t>
@@ -3288,17 +3284,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Randijaur, Lu lm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>688612</v>
+        <v>688413</v>
       </c>
       <c r="R26" t="n">
-        <v>7412681</v>
+        <v>7412919</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3322,22 +3318,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:56</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3353,27 +3339,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320487</t>
+          <t>https://artportalen.se/Sighting/137104048</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136453653</v>
+        <v>136320487</v>
       </c>
       <c r="B27" t="n">
-        <v>93409</v>
+        <v>93407</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3398,20 +3384,35 @@
           <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>688484</v>
+        <v>688612</v>
       </c>
       <c r="R27" t="n">
-        <v>7412889</v>
+        <v>7412681</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3438,24 +3439,35 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>12:56</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -3466,16 +3478,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453653</t>
+          <t>https://artportalen.se/Sighting/136320487</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136453654</v>
+        <v>136453653</v>
       </c>
       <c r="B28" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3507,10 +3519,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>688755</v>
+        <v>688484</v>
       </c>
       <c r="R28" t="n">
-        <v>7412675</v>
+        <v>7412889</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3568,16 +3580,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453654</t>
+          <t>https://artportalen.se/Sighting/136453653</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136814451</v>
+        <v>136453654</v>
       </c>
       <c r="B29" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3605,17 +3617,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>688675</v>
+        <v>688755</v>
       </c>
       <c r="R29" t="n">
-        <v>7412729</v>
+        <v>7412675</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3642,19 +3654,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>11:17</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3669,27 +3671,27 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814451</t>
+          <t>https://artportalen.se/Sighting/136453654</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136814452</v>
+        <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3721,13 +3723,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>688672</v>
+        <v>688675</v>
       </c>
       <c r="R30" t="n">
-        <v>7412721</v>
+        <v>7412729</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3792,16 +3794,16 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814452</t>
+          <t>https://artportalen.se/Sighting/136814451</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136814454</v>
+        <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3833,10 +3835,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>688682</v>
+        <v>688672</v>
       </c>
       <c r="R31" t="n">
-        <v>7412781</v>
+        <v>7412721</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3868,7 +3870,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3878,7 +3880,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3904,16 +3906,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814454</t>
+          <t>https://artportalen.se/Sighting/136814452</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136814459</v>
+        <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3945,13 +3947,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>688649</v>
+        <v>688682</v>
       </c>
       <c r="R32" t="n">
-        <v>7412806</v>
+        <v>7412781</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3980,7 +3982,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3990,7 +3992,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4016,16 +4018,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814459</t>
+          <t>https://artportalen.se/Sighting/136814454</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136814461</v>
+        <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4057,13 +4059,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>688794</v>
+        <v>688649</v>
       </c>
       <c r="R33" t="n">
-        <v>7413016</v>
+        <v>7412806</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4092,7 +4094,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4102,7 +4104,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4128,16 +4130,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814461</t>
+          <t>https://artportalen.se/Sighting/136814459</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136814463</v>
+        <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4169,13 +4171,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>688692</v>
+        <v>688794</v>
       </c>
       <c r="R34" t="n">
-        <v>7413080</v>
+        <v>7413016</v>
       </c>
       <c r="S34" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4204,7 +4206,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4214,7 +4216,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4240,16 +4242,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814463</t>
+          <t>https://artportalen.se/Sighting/136814461</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136814488</v>
+        <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93409</v>
+        <v>93410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4281,13 +4283,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>688612</v>
+        <v>688692</v>
       </c>
       <c r="R35" t="n">
-        <v>7412693</v>
+        <v>7413080</v>
       </c>
       <c r="S35" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4316,7 +4318,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4326,7 +4328,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4352,16 +4354,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814488</t>
+          <t>https://artportalen.se/Sighting/136814463</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>136320479</v>
+        <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93413</v>
+        <v>93410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4369,37 +4371,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>688599</v>
+        <v>688612</v>
       </c>
       <c r="R36" t="n">
-        <v>7412694</v>
+        <v>7412693</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4428,7 +4430,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4438,7 +4440,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4453,27 +4455,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320479</t>
+          <t>https://artportalen.se/Sighting/136814488</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>136453646</v>
+        <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93415</v>
+        <v>93410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4481,34 +4483,45 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Randijaur, Lu lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>688630</v>
+        <v>688411</v>
       </c>
       <c r="R37" t="n">
-        <v>7413081</v>
+        <v>7412943</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4535,12 +4548,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4549,33 +4562,34 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Tor Tuorda</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453646</t>
+          <t>https://artportalen.se/Sighting/137104180</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>136453647</v>
+        <v>136320479</v>
       </c>
       <c r="B38" t="n">
-        <v>93415</v>
+        <v>93413</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4607,10 +4621,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>688683</v>
+        <v>688599</v>
       </c>
       <c r="R38" t="n">
-        <v>7413083</v>
+        <v>7412694</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4640,9 +4654,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4657,7 +4681,7 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -4668,16 +4692,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453647</t>
+          <t>https://artportalen.se/Sighting/136320479</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>136453648</v>
+        <v>136453646</v>
       </c>
       <c r="B39" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4709,10 +4733,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>688769</v>
+        <v>688630</v>
       </c>
       <c r="R39" t="n">
-        <v>7412925</v>
+        <v>7413081</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4770,16 +4794,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453648</t>
+          <t>https://artportalen.se/Sighting/136453646</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>136453649</v>
+        <v>136453647</v>
       </c>
       <c r="B40" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4811,10 +4835,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>688799</v>
+        <v>688683</v>
       </c>
       <c r="R40" t="n">
-        <v>7412688</v>
+        <v>7413083</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4872,16 +4896,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453649</t>
+          <t>https://artportalen.se/Sighting/136453647</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>136453650</v>
+        <v>136453648</v>
       </c>
       <c r="B41" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4913,10 +4937,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>688746</v>
+        <v>688769</v>
       </c>
       <c r="R41" t="n">
-        <v>7412670</v>
+        <v>7412925</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4974,16 +4998,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453650</t>
+          <t>https://artportalen.se/Sighting/136453648</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>136453651</v>
+        <v>136453649</v>
       </c>
       <c r="B42" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5015,10 +5039,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>688743</v>
+        <v>688799</v>
       </c>
       <c r="R42" t="n">
-        <v>7412560</v>
+        <v>7412688</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5076,16 +5100,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453651</t>
+          <t>https://artportalen.se/Sighting/136453649</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>136814447</v>
+        <v>136453650</v>
       </c>
       <c r="B43" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5113,17 +5137,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>688729</v>
+        <v>688746</v>
       </c>
       <c r="R43" t="n">
-        <v>7412676</v>
+        <v>7412670</v>
       </c>
       <c r="S43" t="n">
-        <v>62</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5150,19 +5174,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5177,27 +5191,27 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814447</t>
+          <t>https://artportalen.se/Sighting/136453650</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>136814458</v>
+        <v>136453651</v>
       </c>
       <c r="B44" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5225,14 +5239,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>688672</v>
+        <v>688743</v>
       </c>
       <c r="R44" t="n">
-        <v>7412830</v>
+        <v>7412560</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5262,19 +5276,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:37</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5289,27 +5293,27 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814458</t>
+          <t>https://artportalen.se/Sighting/136453651</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>136814480</v>
+        <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5341,13 +5345,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>688585</v>
+        <v>688729</v>
       </c>
       <c r="R45" t="n">
-        <v>7412719</v>
+        <v>7412676</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5376,7 +5380,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5386,7 +5390,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5412,16 +5416,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814480</t>
+          <t>https://artportalen.se/Sighting/136814447</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>136814486</v>
+        <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5453,13 +5457,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>688599</v>
+        <v>688672</v>
       </c>
       <c r="R46" t="n">
-        <v>7412701</v>
+        <v>7412830</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5492,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5502,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5524,54 +5528,54 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814486</t>
+          <t>https://artportalen.se/Sighting/136814458</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>136320475</v>
+        <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93417</v>
+        <v>93416</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>688611</v>
+        <v>688585</v>
       </c>
       <c r="R47" t="n">
-        <v>7412650</v>
+        <v>7412719</v>
       </c>
       <c r="S47" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5600,7 +5604,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5610,7 +5614,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:39</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5625,65 +5629,65 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320475</t>
+          <t>https://artportalen.se/Sighting/136814480</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>136320484</v>
+        <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93417</v>
+        <v>93416</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>688632</v>
+        <v>688599</v>
       </c>
       <c r="R48" t="n">
-        <v>7412785</v>
+        <v>7412701</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5712,7 +5716,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5722,7 +5726,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5737,27 +5741,27 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320484</t>
+          <t>https://artportalen.se/Sighting/136814486</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>136814442</v>
+        <v>136320475</v>
       </c>
       <c r="B49" t="n">
-        <v>93419</v>
+        <v>93417</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5785,17 +5789,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>688703</v>
+        <v>688611</v>
       </c>
       <c r="R49" t="n">
-        <v>7412635</v>
+        <v>7412650</v>
       </c>
       <c r="S49" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5824,7 +5828,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5834,7 +5838,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:39</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,27 +5853,27 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814442</t>
+          <t>https://artportalen.se/Sighting/136320475</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>136814481</v>
+        <v>136320484</v>
       </c>
       <c r="B50" t="n">
-        <v>93419</v>
+        <v>93417</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5897,14 +5901,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>688584</v>
+        <v>688632</v>
       </c>
       <c r="R50" t="n">
-        <v>7412718</v>
+        <v>7412785</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5936,7 +5940,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5946,7 +5950,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5961,65 +5965,65 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814481</t>
+          <t>https://artportalen.se/Sighting/136320484</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>136453604</v>
+        <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93427</v>
+        <v>93420</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>688416</v>
+        <v>688703</v>
       </c>
       <c r="R51" t="n">
-        <v>7412828</v>
+        <v>7412635</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6046,9 +6050,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6063,62 +6077,62 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453604</t>
+          <t>https://artportalen.se/Sighting/136814442</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>136453606</v>
+        <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93427</v>
+        <v>93420</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4366</v>
+        <v>4365</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>688676</v>
+        <v>688584</v>
       </c>
       <c r="R52" t="n">
-        <v>7413050</v>
+        <v>7412718</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6148,9 +6162,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6165,27 +6189,27 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453606</t>
+          <t>https://artportalen.se/Sighting/136814481</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>136453608</v>
+        <v>136453604</v>
       </c>
       <c r="B53" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6217,10 +6241,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>688686</v>
+        <v>688416</v>
       </c>
       <c r="R53" t="n">
-        <v>7413083</v>
+        <v>7412828</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6278,16 +6302,16 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453608</t>
+          <t>https://artportalen.se/Sighting/136453604</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>136453610</v>
+        <v>136453606</v>
       </c>
       <c r="B54" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6319,10 +6343,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>688805</v>
+        <v>688676</v>
       </c>
       <c r="R54" t="n">
-        <v>7412528</v>
+        <v>7413050</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6380,16 +6404,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453610</t>
+          <t>https://artportalen.se/Sighting/136453606</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>136814468</v>
+        <v>136453608</v>
       </c>
       <c r="B55" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6417,11 +6441,11 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>688656</v>
+        <v>688686</v>
       </c>
       <c r="R55" t="n">
         <v>7413083</v>
@@ -6454,19 +6478,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:09</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:09</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6481,27 +6495,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814468</t>
+          <t>https://artportalen.se/Sighting/136453608</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>136453589</v>
+        <v>136453610</v>
       </c>
       <c r="B56" t="n">
-        <v>93059</v>
+        <v>93428</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6509,21 +6523,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6533,10 +6547,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>688788</v>
+        <v>688805</v>
       </c>
       <c r="R56" t="n">
-        <v>7412652</v>
+        <v>7412528</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6594,16 +6608,16 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453589</t>
+          <t>https://artportalen.se/Sighting/136453610</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>136453631</v>
+        <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>90711</v>
+        <v>93428</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6611,34 +6625,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4962</v>
+        <v>4366</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>688695</v>
+        <v>688656</v>
       </c>
       <c r="R57" t="n">
-        <v>7412638</v>
+        <v>7413083</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6668,45 +6682,54 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453631</t>
+          <t>https://artportalen.se/Sighting/136814468</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>136453634</v>
+        <v>136453589</v>
       </c>
       <c r="B58" t="n">
-        <v>90711</v>
+        <v>93060</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6714,21 +6737,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4962</v>
+        <v>4745</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6738,10 +6761,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>688382</v>
+        <v>688788</v>
       </c>
       <c r="R58" t="n">
-        <v>7412847</v>
+        <v>7412652</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6799,16 +6822,16 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453634</t>
+          <t>https://artportalen.se/Sighting/136453589</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>136453635</v>
+        <v>136453631</v>
       </c>
       <c r="B59" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6840,10 +6863,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>688661</v>
+        <v>688695</v>
       </c>
       <c r="R59" t="n">
-        <v>7413082</v>
+        <v>7412638</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -6884,6 +6907,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6901,16 +6925,16 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453635</t>
+          <t>https://artportalen.se/Sighting/136453631</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>136453636</v>
+        <v>136453634</v>
       </c>
       <c r="B60" t="n">
-        <v>90711</v>
+        <v>90712</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6942,10 +6966,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>688788</v>
+        <v>688382</v>
       </c>
       <c r="R60" t="n">
-        <v>7412702</v>
+        <v>7412847</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -7003,16 +7027,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453636</t>
+          <t>https://artportalen.se/Sighting/136453634</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>136453592</v>
+        <v>136453635</v>
       </c>
       <c r="B61" t="n">
-        <v>93441</v>
+        <v>90712</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7020,21 +7044,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7044,10 +7068,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>688668</v>
+        <v>688661</v>
       </c>
       <c r="R61" t="n">
-        <v>7413059</v>
+        <v>7413082</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7105,38 +7129,38 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453592</t>
+          <t>https://artportalen.se/Sighting/136453635</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>136320482</v>
+        <v>136453636</v>
       </c>
       <c r="B62" t="n">
-        <v>91469</v>
+        <v>90712</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5685</v>
+        <v>4962</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7146,13 +7170,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>688676</v>
+        <v>688788</v>
       </c>
       <c r="R62" t="n">
-        <v>7412739</v>
+        <v>7412702</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7179,35 +7203,24 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
@@ -7218,38 +7231,38 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320482</t>
+          <t>https://artportalen.se/Sighting/136453636</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>136320483</v>
+        <v>136453592</v>
       </c>
       <c r="B63" t="n">
-        <v>93397</v>
+        <v>93442</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6055</v>
+        <v>5448</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7259,10 +7272,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>688686</v>
+        <v>688668</v>
       </c>
       <c r="R63" t="n">
-        <v>7412816</v>
+        <v>7413059</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7292,19 +7305,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:27</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7319,7 +7322,7 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
@@ -7330,54 +7333,54 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136320483</t>
+          <t>https://artportalen.se/Sighting/136453592</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>136814444</v>
+        <v>136320482</v>
       </c>
       <c r="B64" t="n">
-        <v>93399</v>
+        <v>91469</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6055</v>
+        <v>5685</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>688704</v>
+        <v>688676</v>
       </c>
       <c r="R64" t="n">
-        <v>7412632</v>
+        <v>7412739</v>
       </c>
       <c r="S64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7406,7 +7409,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7416,7 +7419,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7425,33 +7428,34 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814444</t>
+          <t>https://artportalen.se/Sighting/136320482</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>136814473</v>
+        <v>136320483</v>
       </c>
       <c r="B65" t="n">
-        <v>90880</v>
+        <v>93397</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7459,34 +7463,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6276</v>
+        <v>6055</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>688528</v>
+        <v>688686</v>
       </c>
       <c r="R65" t="n">
-        <v>7412947</v>
+        <v>7412816</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -7518,7 +7522,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7528,7 +7532,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7543,27 +7547,27 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814473</t>
+          <t>https://artportalen.se/Sighting/136320483</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>136453557</v>
+        <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>90899</v>
+        <v>93400</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7571,41 +7575,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6286</v>
+        <v>6055</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>688707</v>
+        <v>688704</v>
       </c>
       <c r="R66" t="n">
-        <v>7412748</v>
+        <v>7412632</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7635,45 +7632,54 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453557</t>
+          <t>https://artportalen.se/Sighting/136814444</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>136453561</v>
+        <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90899</v>
+        <v>90881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7681,45 +7687,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6286</v>
+        <v>6276</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>688727</v>
+        <v>688528</v>
       </c>
       <c r="R67" t="n">
-        <v>7412612</v>
+        <v>7412947</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -7749,45 +7744,54 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453561</t>
+          <t>https://artportalen.se/Sighting/136814473</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136814453</v>
+        <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7812,17 +7816,24 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>688671</v>
+        <v>688707</v>
       </c>
       <c r="R68" t="n">
-        <v>7412721</v>
+        <v>7412748</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -7852,54 +7863,45 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>11:27</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814453</t>
+          <t>https://artportalen.se/Sighting/136453557</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>136814456</v>
+        <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7924,17 +7926,28 @@
           <t>(Fr.) Quél.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>688687</v>
+        <v>688727</v>
       </c>
       <c r="R69" t="n">
-        <v>7412760</v>
+        <v>7412612</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -7964,54 +7977,45 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814456</t>
+          <t>https://artportalen.se/Sighting/136453561</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>136814469</v>
+        <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90899</v>
+        <v>90900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8043,10 +8047,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>688590</v>
+        <v>688671</v>
       </c>
       <c r="R70" t="n">
-        <v>7413075</v>
+        <v>7412721</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8078,7 +8082,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8088,7 +8092,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8114,51 +8118,51 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814469</t>
+          <t>https://artportalen.se/Sighting/136814453</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>136453628</v>
+        <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>79506</v>
+        <v>90900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6434</v>
+        <v>6286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>688754</v>
+        <v>688687</v>
       </c>
       <c r="R71" t="n">
-        <v>7412697</v>
+        <v>7412760</v>
       </c>
       <c r="S71" t="n">
         <v>5</v>
@@ -8188,9 +8192,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8205,62 +8219,62 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453628</t>
+          <t>https://artportalen.se/Sighting/136814456</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>136453655</v>
+        <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>78885</v>
+        <v>90900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6437</v>
+        <v>6286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>688481</v>
+        <v>688590</v>
       </c>
       <c r="R72" t="n">
-        <v>7412888</v>
+        <v>7413075</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8290,9 +8304,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8307,49 +8331,49 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453655</t>
+          <t>https://artportalen.se/Sighting/136814469</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>136453656</v>
+        <v>136453628</v>
       </c>
       <c r="B73" t="n">
-        <v>78885</v>
+        <v>79507</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8359,10 +8383,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>688564</v>
+        <v>688754</v>
       </c>
       <c r="R73" t="n">
-        <v>7413072</v>
+        <v>7412697</v>
       </c>
       <c r="S73" t="n">
         <v>5</v>
@@ -8420,16 +8444,16 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453656</t>
+          <t>https://artportalen.se/Sighting/136453628</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>136814474</v>
+        <v>136453655</v>
       </c>
       <c r="B74" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8457,14 +8481,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>688530</v>
+        <v>688481</v>
       </c>
       <c r="R74" t="n">
-        <v>7412946</v>
+        <v>7412888</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8494,19 +8518,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>13:49</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>13:49</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8521,27 +8535,27 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814474</t>
+          <t>https://artportalen.se/Sighting/136453655</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>136814478</v>
+        <v>136453656</v>
       </c>
       <c r="B75" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8569,14 +8583,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>688614</v>
+        <v>688564</v>
       </c>
       <c r="R75" t="n">
-        <v>7412854</v>
+        <v>7413072</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8606,19 +8620,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>14:00</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8633,27 +8637,27 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814478</t>
+          <t>https://artportalen.se/Sighting/136453656</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>136814475</v>
+        <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>79239</v>
+        <v>78886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8661,21 +8665,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8685,10 +8689,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>688543</v>
+        <v>688530</v>
       </c>
       <c r="R76" t="n">
-        <v>7412924</v>
+        <v>7412946</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8720,7 +8724,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8730,7 +8734,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8756,16 +8760,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814475</t>
+          <t>https://artportalen.se/Sighting/136814474</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136453555</v>
+        <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>80101</v>
+        <v>78886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8773,34 +8777,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>688644</v>
+        <v>688614</v>
       </c>
       <c r="R77" t="n">
-        <v>7413032</v>
+        <v>7412854</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8830,9 +8834,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8847,27 +8861,27 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453555</t>
+          <t>https://artportalen.se/Sighting/136814478</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136814467</v>
+        <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>80101</v>
+        <v>79240</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8875,21 +8889,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8899,10 +8913,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>688654</v>
+        <v>688543</v>
       </c>
       <c r="R78" t="n">
-        <v>7413104</v>
+        <v>7412924</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8934,7 +8948,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8944,7 +8958,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8970,16 +8984,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814467</t>
+          <t>https://artportalen.se/Sighting/136814475</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>136814477</v>
+        <v>136453555</v>
       </c>
       <c r="B79" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9007,14 +9021,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>688614</v>
+        <v>688644</v>
       </c>
       <c r="R79" t="n">
-        <v>7412854</v>
+        <v>7413032</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9044,19 +9058,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>13:59</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>13:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9071,62 +9075,62 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814477</t>
+          <t>https://artportalen.se/Sighting/136453555</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136453629</v>
+        <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80601</v>
+        <v>80102</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6461</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>688689</v>
+        <v>688654</v>
       </c>
       <c r="R80" t="n">
-        <v>7413053</v>
+        <v>7413104</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -9156,9 +9160,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9173,27 +9187,27 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453629</t>
+          <t>https://artportalen.se/Sighting/136814467</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136814466</v>
+        <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>58169</v>
+        <v>80102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9201,21 +9215,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9225,10 +9239,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>688654</v>
+        <v>688614</v>
       </c>
       <c r="R81" t="n">
-        <v>7413103</v>
+        <v>7412854</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9260,7 +9274,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9270,7 +9284,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9296,55 +9310,51 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814466</t>
+          <t>https://artportalen.se/Sighting/136814477</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136453641</v>
+        <v>136453629</v>
       </c>
       <c r="B82" t="n">
-        <v>58112</v>
+        <v>80602</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103031</v>
+        <v>6461</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>688728</v>
+        <v>688689</v>
       </c>
       <c r="R82" t="n">
-        <v>7412723</v>
+        <v>7413053</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9402,16 +9412,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453641</t>
+          <t>https://artportalen.se/Sighting/136453629</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136814455</v>
+        <v>136814466</v>
       </c>
       <c r="B83" t="n">
-        <v>58112</v>
+        <v>58169</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9419,21 +9429,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103031</v>
+        <v>103021</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9443,13 +9453,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>688685</v>
+        <v>688654</v>
       </c>
       <c r="R83" t="n">
-        <v>7412758</v>
+        <v>7413103</v>
       </c>
       <c r="S83" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9478,7 +9488,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9488,7 +9498,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9514,51 +9524,55 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814455</t>
+          <t>https://artportalen.se/Sighting/136814466</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>136453616</v>
+        <v>136453641</v>
       </c>
       <c r="B84" t="n">
-        <v>98229</v>
+        <v>58112</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>688676</v>
+        <v>688728</v>
       </c>
       <c r="R84" t="n">
-        <v>7412815</v>
+        <v>7412723</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -9616,54 +9630,54 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453616</t>
+          <t>https://artportalen.se/Sighting/136453641</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>136453618</v>
+        <v>136814455</v>
       </c>
       <c r="B85" t="n">
-        <v>98229</v>
+        <v>58112</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>688794</v>
+        <v>688685</v>
       </c>
       <c r="R85" t="n">
-        <v>7412706</v>
+        <v>7412758</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9690,9 +9704,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9707,27 +9731,27 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453618</t>
+          <t>https://artportalen.se/Sighting/136814455</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136453620</v>
+        <v>136453616</v>
       </c>
       <c r="B86" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9759,10 +9783,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>688698</v>
+        <v>688676</v>
       </c>
       <c r="R86" t="n">
-        <v>7412629</v>
+        <v>7412815</v>
       </c>
       <c r="S86" t="n">
         <v>5</v>
@@ -9820,16 +9844,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453620</t>
+          <t>https://artportalen.se/Sighting/136453616</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136453622</v>
+        <v>136453618</v>
       </c>
       <c r="B87" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9861,10 +9885,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>688724</v>
+        <v>688794</v>
       </c>
       <c r="R87" t="n">
-        <v>7412621</v>
+        <v>7412706</v>
       </c>
       <c r="S87" t="n">
         <v>5</v>
@@ -9922,16 +9946,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453622</t>
+          <t>https://artportalen.se/Sighting/136453618</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>136453623</v>
+        <v>136453620</v>
       </c>
       <c r="B88" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9963,10 +9987,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>688725</v>
+        <v>688698</v>
       </c>
       <c r="R88" t="n">
-        <v>7412597</v>
+        <v>7412629</v>
       </c>
       <c r="S88" t="n">
         <v>5</v>
@@ -10024,16 +10048,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453623</t>
+          <t>https://artportalen.se/Sighting/136453620</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>136814457</v>
+        <v>136453622</v>
       </c>
       <c r="B89" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10061,14 +10085,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>688687</v>
+        <v>688724</v>
       </c>
       <c r="R89" t="n">
-        <v>7412821</v>
+        <v>7412621</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -10098,19 +10122,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>11:34</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>11:34</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10125,65 +10139,65 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814457</t>
+          <t>https://artportalen.se/Sighting/136453622</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136814464</v>
+        <v>136453623</v>
       </c>
       <c r="B90" t="n">
-        <v>80072</v>
+        <v>98230</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>688651</v>
+        <v>688725</v>
       </c>
       <c r="R90" t="n">
-        <v>7413103</v>
+        <v>7412597</v>
       </c>
       <c r="S90" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10210,19 +10224,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>12:59</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>12:59</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10237,49 +10241,49 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814464</t>
+          <t>https://artportalen.se/Sighting/136453623</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136814476</v>
+        <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>80072</v>
+        <v>98230</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10289,10 +10293,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>688618</v>
+        <v>688687</v>
       </c>
       <c r="R91" t="n">
-        <v>7412849</v>
+        <v>7412821</v>
       </c>
       <c r="S91" t="n">
         <v>5</v>
@@ -10324,7 +10328,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10334,7 +10338,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10360,16 +10364,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814476</t>
+          <t>https://artportalen.se/Sighting/136814457</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136814485</v>
+        <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10401,13 +10405,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>688579</v>
+        <v>688651</v>
       </c>
       <c r="R92" t="n">
-        <v>7412740</v>
+        <v>7413103</v>
       </c>
       <c r="S92" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10436,7 +10440,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10446,7 +10450,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10472,16 +10476,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814485</t>
+          <t>https://artportalen.se/Sighting/136814464</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136814487</v>
+        <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10513,13 +10517,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>688615</v>
+        <v>688618</v>
       </c>
       <c r="R93" t="n">
-        <v>7412698</v>
+        <v>7412849</v>
       </c>
       <c r="S93" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10548,7 +10552,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10558,7 +10562,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10584,38 +10588,38 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814487</t>
+          <t>https://artportalen.se/Sighting/136814476</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136814482</v>
+        <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>93446</v>
+        <v>80073</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>232140</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10625,13 +10629,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>688585</v>
+        <v>688579</v>
       </c>
       <c r="R94" t="n">
-        <v>7412723</v>
+        <v>7412740</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10660,7 +10664,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10670,7 +10674,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10696,16 +10700,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814482</t>
+          <t>https://artportalen.se/Sighting/136814485</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>136453575</v>
+        <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>79505</v>
+        <v>80073</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10713,37 +10717,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>688561</v>
+        <v>688615</v>
       </c>
       <c r="R95" t="n">
-        <v>7413047</v>
+        <v>7412698</v>
       </c>
       <c r="S95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10770,9 +10774,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10787,62 +10801,62 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453575</t>
+          <t>https://artportalen.se/Sighting/136814487</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>136453577</v>
+        <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>79505</v>
+        <v>93447</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>260591</v>
+        <v>232140</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Várditjåhkkå, Lu lm</t>
+          <t>Várditjåkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>688702</v>
+        <v>688585</v>
       </c>
       <c r="R96" t="n">
-        <v>7412735</v>
+        <v>7412723</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -10872,9 +10886,19 @@
           <t>2026-09-03</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>14:14</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10889,27 +10913,27 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Linda Nordström</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453577</t>
+          <t>https://artportalen.se/Sighting/136814482</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>136453579</v>
+        <v>136453575</v>
       </c>
       <c r="B97" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10941,10 +10965,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>688781</v>
+        <v>688561</v>
       </c>
       <c r="R97" t="n">
-        <v>7412725</v>
+        <v>7413047</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -11002,16 +11026,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453579</t>
+          <t>https://artportalen.se/Sighting/136453575</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>136453581</v>
+        <v>136453577</v>
       </c>
       <c r="B98" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11043,10 +11067,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>688787</v>
+        <v>688702</v>
       </c>
       <c r="R98" t="n">
-        <v>7412707</v>
+        <v>7412735</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -11104,16 +11128,16 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453581</t>
+          <t>https://artportalen.se/Sighting/136453577</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>136453583</v>
+        <v>136453579</v>
       </c>
       <c r="B99" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11145,10 +11169,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>688757</v>
+        <v>688781</v>
       </c>
       <c r="R99" t="n">
-        <v>7412706</v>
+        <v>7412725</v>
       </c>
       <c r="S99" t="n">
         <v>5</v>
@@ -11206,16 +11230,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453583</t>
+          <t>https://artportalen.se/Sighting/136453579</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136453585</v>
+        <v>136453581</v>
       </c>
       <c r="B100" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11247,10 +11271,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>688699</v>
+        <v>688787</v>
       </c>
       <c r="R100" t="n">
-        <v>7412642</v>
+        <v>7412707</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -11308,16 +11332,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453585</t>
+          <t>https://artportalen.se/Sighting/136453581</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>136453587</v>
+        <v>136453583</v>
       </c>
       <c r="B101" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11349,10 +11373,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>688715</v>
+        <v>688757</v>
       </c>
       <c r="R101" t="n">
-        <v>7412627</v>
+        <v>7412706</v>
       </c>
       <c r="S101" t="n">
         <v>5</v>
@@ -11410,16 +11434,16 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136453587</t>
+          <t>https://artportalen.se/Sighting/136453583</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>136814446</v>
+        <v>136453585</v>
       </c>
       <c r="B102" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11447,14 +11471,14 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>688717</v>
+        <v>688699</v>
       </c>
       <c r="R102" t="n">
-        <v>7412657</v>
+        <v>7412642</v>
       </c>
       <c r="S102" t="n">
         <v>5</v>
@@ -11484,19 +11508,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>10:43</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>10:43</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11511,27 +11525,27 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814446</t>
+          <t>https://artportalen.se/Sighting/136453585</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>136814472</v>
+        <v>136453587</v>
       </c>
       <c r="B103" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11559,14 +11573,14 @@
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Várditjåkkå, Lu lm</t>
+          <t>Várditjåhkkå, Lu lm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>688530</v>
+        <v>688715</v>
       </c>
       <c r="R103" t="n">
-        <v>7412959</v>
+        <v>7412627</v>
       </c>
       <c r="S103" t="n">
         <v>5</v>
@@ -11596,19 +11610,9 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:41</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:41</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11623,27 +11627,27 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Linda Nordström</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136814472</t>
+          <t>https://artportalen.se/Sighting/136453587</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>136814479</v>
+        <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>93436</v>
+        <v>79506</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11651,21 +11655,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6331648</v>
+        <v>260591</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Nordtaggsvamp</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon aquiloniniger</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>A.M.Ainsw. &amp; Svantesson</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11675,10 +11679,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>688585</v>
+        <v>688717</v>
       </c>
       <c r="R104" t="n">
-        <v>7412719</v>
+        <v>7412657</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -11710,7 +11714,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11720,7 +11724,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11729,7 +11733,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11746,6 +11749,231 @@
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814446</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>136814472</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>688530</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7412959</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136814472</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>136814479</v>
+      </c>
+      <c r="B106" t="n">
+        <v>93437</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6331648</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Nordtaggsvamp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Phellodon aquiloniniger</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>A.M.Ainsw. &amp; Svantesson</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Várditjåkkå, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>688585</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7412719</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF106" t="inlineStr"/>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Linda Nordström</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136814479</t>
         </is>
@@ -11856,6 +12084,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1359,7 +1359,7 @@
         <v>136453642</v>
       </c>
       <c r="B8" t="n">
-        <v>92297</v>
+        <v>92303</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91122</v>
+        <v>91128</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1797,7 +1797,7 @@
         <v>136453551</v>
       </c>
       <c r="B12" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         <v>136453553</v>
       </c>
       <c r="B13" t="n">
-        <v>92040</v>
+        <v>92046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>136453594</v>
       </c>
       <c r="B14" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2103,7 +2103,7 @@
         <v>136453596</v>
       </c>
       <c r="B15" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
         <v>136453598</v>
       </c>
       <c r="B16" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,7 +2307,7 @@
         <v>136453600</v>
       </c>
       <c r="B17" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136453602</v>
       </c>
       <c r="B18" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2511,7 +2511,7 @@
         <v>136453637</v>
       </c>
       <c r="B19" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>136453640</v>
       </c>
       <c r="B20" t="n">
-        <v>87508</v>
+        <v>87514</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>136453625</v>
       </c>
       <c r="B22" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>136453626</v>
       </c>
       <c r="B23" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         <v>136453627</v>
       </c>
       <c r="B24" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93408</v>
+        <v>93414</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3487,7 +3487,7 @@
         <v>136453653</v>
       </c>
       <c r="B28" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
         <v>136453654</v>
       </c>
       <c r="B29" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93410</v>
+        <v>93416</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>136453646</v>
       </c>
       <c r="B39" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         <v>136453647</v>
       </c>
       <c r="B40" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4905,7 +4905,7 @@
         <v>136453648</v>
       </c>
       <c r="B41" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5007,7 +5007,7 @@
         <v>136453649</v>
       </c>
       <c r="B42" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5109,7 +5109,7 @@
         <v>136453650</v>
       </c>
       <c r="B43" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5211,7 +5211,7 @@
         <v>136453651</v>
       </c>
       <c r="B44" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93420</v>
+        <v>93426</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>136453604</v>
       </c>
       <c r="B53" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         <v>136453606</v>
       </c>
       <c r="B54" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>136453608</v>
       </c>
       <c r="B55" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>136453610</v>
       </c>
       <c r="B56" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136453589</v>
       </c>
       <c r="B58" t="n">
-        <v>93060</v>
+        <v>93066</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         <v>136453631</v>
       </c>
       <c r="B59" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>136453634</v>
       </c>
       <c r="B60" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>136453635</v>
       </c>
       <c r="B61" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7138,7 +7138,7 @@
         <v>136453636</v>
       </c>
       <c r="B62" t="n">
-        <v>90712</v>
+        <v>90718</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7240,7 +7240,7 @@
         <v>136453592</v>
       </c>
       <c r="B63" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93400</v>
+        <v>93406</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90881</v>
+        <v>90887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90900</v>
+        <v>90906</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>136453616</v>
       </c>
       <c r="B86" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9853,7 +9853,7 @@
         <v>136453618</v>
       </c>
       <c r="B87" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9955,7 +9955,7 @@
         <v>136453620</v>
       </c>
       <c r="B88" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>136453622</v>
       </c>
       <c r="B89" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>136453623</v>
       </c>
       <c r="B90" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93437</v>
+        <v>93443</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91128</v>
+        <v>91132</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93447</v>
+        <v>93451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93414</v>
+        <v>93418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93416</v>
+        <v>93420</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93426</v>
+        <v>93430</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93406</v>
+        <v>93410</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90887</v>
+        <v>90891</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90906</v>
+        <v>90910</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>78886</v>
+        <v>78888</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>79240</v>
+        <v>79242</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98236</v>
+        <v>98240</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93453</v>
+        <v>93457</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>136814472</v>
       </c>
       <c r="B105" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93443</v>
+        <v>93447</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -10261,7 +10261,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91132</v>
+        <v>91134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93418</v>
+        <v>93420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93420</v>
+        <v>93422</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93430</v>
+        <v>93432</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93410</v>
+        <v>93412</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90891</v>
+        <v>90893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90910</v>
+        <v>90912</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93457</v>
+        <v>93459</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>136814472</v>
       </c>
       <c r="B105" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91134</v>
+        <v>91147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93453</v>
+        <v>93466</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93420</v>
+        <v>93433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93422</v>
+        <v>93435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93432</v>
+        <v>93445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93412</v>
+        <v>93425</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90893</v>
+        <v>90906</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90912</v>
+        <v>90925</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>78891</v>
+        <v>78904</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>79245</v>
+        <v>79258</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>136814466</v>
       </c>
       <c r="B83" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>136814455</v>
       </c>
       <c r="B85" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98244</v>
+        <v>98257</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93459</v>
+        <v>93472</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>136814472</v>
       </c>
       <c r="B105" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93449</v>
+        <v>93462</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91147</v>
+        <v>91149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93466</v>
+        <v>93467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93433</v>
+        <v>93434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,7 +3803,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3915,7 +3915,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4139,7 +4139,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93435</v>
+        <v>93436</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5313,7 +5313,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5537,7 +5537,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93445</v>
+        <v>93446</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6617,7 +6617,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93425</v>
+        <v>93426</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90906</v>
+        <v>90908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7901,7 +7901,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90925</v>
+        <v>90927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9095,7 +9095,7 @@
         <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9207,7 +9207,7 @@
         <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>136814466</v>
       </c>
       <c r="B83" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>136814455</v>
       </c>
       <c r="B85" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10597,7 +10597,7 @@
         <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10709,7 +10709,7 @@
         <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10821,7 +10821,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93472</v>
+        <v>93473</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>136814472</v>
       </c>
       <c r="B105" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11871,7 +11871,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93462</v>
+        <v>93463</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -3276,11 +3276,7 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -4506,11 +4502,7 @@
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91149</v>
+        <v>91152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93467</v>
+        <v>93470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93434</v>
+        <v>93437</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93446</v>
+        <v>93449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90908</v>
+        <v>90911</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90927</v>
+        <v>90930</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93473</v>
+        <v>93476</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93463</v>
+        <v>93466</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91152</v>
+        <v>91162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93470</v>
+        <v>93480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93437</v>
+        <v>93447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93439</v>
+        <v>93449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93449</v>
+        <v>93459</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93429</v>
+        <v>93439</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90911</v>
+        <v>90921</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90930</v>
+        <v>90940</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>136814466</v>
       </c>
       <c r="B83" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136814455</v>
       </c>
       <c r="B85" t="n">
-        <v>58127</v>
+        <v>58137</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93476</v>
+        <v>93486</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136814472</v>
       </c>
       <c r="B105" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93466</v>
+        <v>93476</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91162</v>
+        <v>91163</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93480</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93447</v>
+        <v>93448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93449</v>
+        <v>93450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93459</v>
+        <v>93460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90940</v>
+        <v>90941</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93486</v>
+        <v>93487</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93476</v>
+        <v>93477</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91163</v>
+        <v>91166</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93448</v>
+        <v>93453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93450</v>
+        <v>93455</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93460</v>
+        <v>93465</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90922</v>
+        <v>90925</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90941</v>
+        <v>90944</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>136814466</v>
       </c>
       <c r="B83" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136814455</v>
       </c>
       <c r="B85" t="n">
-        <v>58137</v>
+        <v>58138</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93487</v>
+        <v>93492</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136814472</v>
       </c>
       <c r="B105" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93477</v>
+        <v>93482</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91166</v>
+        <v>91168</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93486</v>
+        <v>93488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93453</v>
+        <v>93455</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93455</v>
+        <v>93457</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93465</v>
+        <v>93467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90944</v>
+        <v>90946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93492</v>
+        <v>93494</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93482</v>
+        <v>93484</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>

--- a/artfynd/A 3821-2026 artfynd.xlsx
+++ b/artfynd/A 3821-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>136814462</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136814470</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
         <v>136814445</v>
       </c>
       <c r="B9" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>136814450</v>
       </c>
       <c r="B10" t="n">
-        <v>91168</v>
+        <v>91173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>136814441</v>
       </c>
       <c r="B11" t="n">
-        <v>93488</v>
+        <v>93494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>136814460</v>
       </c>
       <c r="B25" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3245,7 +3245,7 @@
         <v>137104048</v>
       </c>
       <c r="B26" t="n">
-        <v>93455</v>
+        <v>93461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3687,7 +3687,7 @@
         <v>136814451</v>
       </c>
       <c r="B30" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>136814452</v>
       </c>
       <c r="B31" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3911,7 +3911,7 @@
         <v>136814454</v>
       </c>
       <c r="B32" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4023,7 +4023,7 @@
         <v>136814459</v>
       </c>
       <c r="B33" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         <v>136814461</v>
       </c>
       <c r="B34" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>136814463</v>
       </c>
       <c r="B35" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         <v>136814488</v>
       </c>
       <c r="B36" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         <v>137104180</v>
       </c>
       <c r="B37" t="n">
-        <v>93457</v>
+        <v>93463</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>136814447</v>
       </c>
       <c r="B45" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>136814458</v>
       </c>
       <c r="B46" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>136814480</v>
       </c>
       <c r="B47" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>136814486</v>
       </c>
       <c r="B48" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>136814442</v>
       </c>
       <c r="B51" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>136814481</v>
       </c>
       <c r="B52" t="n">
-        <v>93467</v>
+        <v>93473</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6609,7 +6609,7 @@
         <v>136814468</v>
       </c>
       <c r="B57" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>136814444</v>
       </c>
       <c r="B66" t="n">
-        <v>93447</v>
+        <v>93453</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7671,7 +7671,7 @@
         <v>136814473</v>
       </c>
       <c r="B67" t="n">
-        <v>90925</v>
+        <v>90930</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>136453557</v>
       </c>
       <c r="B68" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7893,7 +7893,7 @@
         <v>136453561</v>
       </c>
       <c r="B69" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         <v>136814453</v>
       </c>
       <c r="B70" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         <v>136814456</v>
       </c>
       <c r="B71" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>136814469</v>
       </c>
       <c r="B72" t="n">
-        <v>90946</v>
+        <v>90951</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8649,7 +8649,7 @@
         <v>136814474</v>
       </c>
       <c r="B76" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>136814478</v>
       </c>
       <c r="B77" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         <v>136814475</v>
       </c>
       <c r="B78" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9087,7 +9087,7 @@
         <v>136814467</v>
       </c>
       <c r="B80" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>136814477</v>
       </c>
       <c r="B81" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         <v>136814466</v>
       </c>
       <c r="B83" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136814455</v>
       </c>
       <c r="B85" t="n">
-        <v>58138</v>
+        <v>58139</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10253,7 +10253,7 @@
         <v>136814457</v>
       </c>
       <c r="B91" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10365,7 +10365,7 @@
         <v>136814464</v>
       </c>
       <c r="B92" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>136814476</v>
       </c>
       <c r="B93" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10589,7 +10589,7 @@
         <v>136814485</v>
       </c>
       <c r="B94" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         <v>136814487</v>
       </c>
       <c r="B95" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10813,7 +10813,7 @@
         <v>136814482</v>
       </c>
       <c r="B96" t="n">
-        <v>93494</v>
+        <v>93500</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>136814446</v>
       </c>
       <c r="B104" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>136814472</v>
       </c>
       <c r="B105" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>136814479</v>
       </c>
       <c r="B106" t="n">
-        <v>93484</v>
+        <v>93490</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
